--- a/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Design Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FBC450-953B-4D6B-87E8-AB4420885AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FEBA13-AFEF-40CF-8D6A-F515C5CF2390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="1332" windowWidth="18684" windowHeight="10992" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="238">
   <si>
     <t>Length_f</t>
   </si>
@@ -1071,9 +1071,6 @@
   </si>
   <si>
     <t>Prop_Dia</t>
-  </si>
-  <si>
-    <t>Submersible</t>
   </si>
   <si>
     <t>JetSubmersible</t>
@@ -3337,7 +3334,7 @@
     </row>
     <row r="2" spans="1:48">
       <c r="A2" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>208</v>
@@ -3443,46 +3440,48 @@
         <v>0</v>
       </c>
       <c r="AI2" s="4">
-        <v>11.69</v>
+        <v>75</v>
       </c>
       <c r="AJ2" s="4">
-        <v>23.385000000000002</v>
+        <f>2*AI2</f>
+        <v>150</v>
       </c>
       <c r="AK2" s="4">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL2" s="4">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AM2" s="4">
-        <v>11.31</v>
+        <v>40</v>
       </c>
       <c r="AN2" s="4">
-        <v>2.2080000000000002</v>
+        <f>(2/3)*((2*AI2)/((SQRT(AK2*AI2))*(1+AL2)))*(1+AL2+AL2^2)/(1+AL2)</f>
+        <v>8.0605786359720426</v>
       </c>
       <c r="AO2" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="AP2" s="4">
-        <v>11.69</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="4">
-        <v>23.385000000000002</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="4">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AT2" s="4">
-        <v>11.31</v>
+        <v>0</v>
       </c>
       <c r="AU2" s="4">
-        <v>2.2080000000000002</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="4">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:48" s="22" customFormat="1"/>
@@ -3818,14 +3817,14 @@
       <c r="AP2" s="29">
         <v>2.1329999999999998E-2</v>
       </c>
-      <c r="AQ2" s="10" t="s">
-        <v>180</v>
+      <c r="AQ2" s="10">
+        <v>0</v>
       </c>
       <c r="AR2" s="10">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AT2" s="10">
         <v>0</v>
@@ -3845,14 +3844,14 @@
       <c r="AY2" s="10">
         <v>0.3</v>
       </c>
-      <c r="AZ2" s="10" t="s">
-        <v>180</v>
+      <c r="AZ2" s="10">
+        <v>0</v>
       </c>
       <c r="BA2" s="10">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="BB2" s="10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:54" s="23" customFormat="1"/>
@@ -3936,16 +3935,16 @@
         <v>237</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3954,38 +3953,38 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <f>M2*N2*O2*P2</f>
-        <v>221.61599999999999</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18" s="21" customFormat="1"/>

--- a/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="1" state="visible" r:id="rId2"/>
@@ -2839,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>42</v>
@@ -3453,7 +3453,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>7500</v>
+        <v>9500</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>0.77</v>

--- a/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
@@ -1,29 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Design Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85978DB0-2775-462B-8CCE-E2F5ECB74B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Variable Reference" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Main_Input" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Airfoil_Data" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Propulsion" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Lists" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Geometry Reference" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Variable Reference" sheetId="1" r:id="rId1"/>
+    <sheet name="Main_Input" sheetId="2" r:id="rId2"/>
+    <sheet name="Airfoil_Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Propulsion" sheetId="4" r:id="rId4"/>
+    <sheet name="Lists" sheetId="5" r:id="rId5"/>
+    <sheet name="Geometry Reference" sheetId="6" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
-    <definedName function="false" hidden="false" name="MATERIALS" vbProcedure="false">#REF!</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="MATERIALS" vbProcedure="false">#REF!</definedName>
+    <definedName name="MATERIALS" localSheetId="0">#REF!</definedName>
+    <definedName name="MATERIALS">#REF!</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -31,17 +44,17 @@
 </workbook>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author> </author>
+    <author/>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -59,16 +72,16 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Units:  lbf
+          <t>Units:  lbf
 Only input values if jet engine, otherwise input "0"</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -86,16 +99,16 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Units:  (lb/hr/lb)
+          <t>Units:  (lb/hr/lb)
 Only input values if jet engine, otherwise input "0"</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -113,16 +126,16 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Units:  lbf
+          <t>Units:  lbf
 Only input values if jet engine, otherwise input "0"</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -140,16 +153,16 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Units:  (lb/hr/lb)
+          <t>Units:  (lb/hr/lb)
 Only input values if jet engine, otherwise input "0"</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -167,15 +180,15 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Value from 0 to 1 representing percent loss (i.e. 20% = 0.2)</t>
+          <t>Value from 0 to 1 representing percent loss (i.e. 20% = 0.2)</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -199,11 +212,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -226,11 +239,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -248,7 +261,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Value from 0 to 1 representing percent propeller efficiency (i.e. 70% = 0.7)</t>
+          <t>Value from 0 to 1 representing percent propeller efficiency (i.e. 70% = 0.7)</t>
         </r>
       </text>
     </comment>
@@ -257,93 +270,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="238">
-  <si>
-    <t xml:space="preserve">Worksheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main_Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User defined configuration number label.  Used to differentiate different designs or trade study variations in designs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aircraft Type. Used for calculating empty weight fraction based on models from Raymer Table 6.1 &amp; 6.2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design altitude.  Utilized to find standard atmosphere properties in model via the atmos function.  Value is typically left at sea level for conceptual design, but can be selected to represent the most prevalent or important mission altitude expected.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate of designed Mach. Used to calculate Reynolds number for model analysis of skin friction drag.  Value should be selected to represent the most prevalent or important mission mach expected.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max mach for design.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length of fuselage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maxium diameter of fuselage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuselage fineness ratio.  Determined by dividing fuselage length by fuselage diameter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ft^2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum fuselage cross-section area.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuselage base drag cross section area.  Determined by finding the cross section in the aft portion of the fuselage where the departure angle of the fuselage contour is &gt; 20 deg.  If this never occurs, then this value is zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wetted area of fuselage equal to the total exposed surface area of the fuselage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuselage interference factor.  Default value is 1.0. for basic streamlined tube fuselage.  Can be &gt; 1.0 if significant fuselage protrusions exist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emperical Wave Drag Factor.  Example valuse:  1 = Ideal Sears-Haack Body, Typcial range for supersonic aircraft is 1.8 - 2.2 for clean, smoothly blended contoured design, 2.5 - 3 = Bumpy volume distribution.  An F-15 has an EWD around 2.9.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wing planform area.  Projected 2-D area of the entire wing to include portions "hidden" within fuselage.  This area is used as the nondimensionalization scaling reference for all aerodynamic coefficients.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="248">
+  <si>
+    <t>Worksheet</t>
+  </si>
+  <si>
+    <t>Variable Name</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Main_Input</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>User defined configuration number label.  Used to differentiate different designs or trade study variations in designs.</t>
+  </si>
+  <si>
+    <t>Aircraft Type. Used for calculating empty weight fraction based on models from Raymer Table 6.1 &amp; 6.2.</t>
+  </si>
+  <si>
+    <t>ft</t>
+  </si>
+  <si>
+    <t>Design altitude.  Utilized to find standard atmosphere properties in model via the atmos function.  Value is typically left at sea level for conceptual design, but can be selected to represent the most prevalent or important mission altitude expected.</t>
+  </si>
+  <si>
+    <t>Estimate of designed Mach. Used to calculate Reynolds number for model analysis of skin friction drag.  Value should be selected to represent the most prevalent or important mission mach expected.</t>
+  </si>
+  <si>
+    <t>Max mach for design.</t>
+  </si>
+  <si>
+    <t>Length of fuselage.</t>
+  </si>
+  <si>
+    <t>Maxium diameter of fuselage.</t>
+  </si>
+  <si>
+    <t>Fuselage fineness ratio.  Determined by dividing fuselage length by fuselage diameter.</t>
+  </si>
+  <si>
+    <t>ft^2</t>
+  </si>
+  <si>
+    <t>Maximum fuselage cross-section area.</t>
+  </si>
+  <si>
+    <t>Fuselage base drag cross section area.  Determined by finding the cross section in the aft portion of the fuselage where the departure angle of the fuselage contour is &gt; 20 deg.  If this never occurs, then this value is zero.</t>
+  </si>
+  <si>
+    <t>Wetted area of fuselage equal to the total exposed surface area of the fuselage.</t>
+  </si>
+  <si>
+    <t>Fuselage interference factor.  Default value is 1.0. for basic streamlined tube fuselage.  Can be &gt; 1.0 if significant fuselage protrusions exist.</t>
+  </si>
+  <si>
+    <t>Emperical Wave Drag Factor.  Example valuse:  1 = Ideal Sears-Haack Body, Typcial range for supersonic aircraft is 1.8 - 2.2 for clean, smoothly blended contoured design, 2.5 - 3 = Bumpy volume distribution.  An F-15 has an EWD around 2.9.</t>
+  </si>
+  <si>
+    <t>Wing planform area.  Projected 2-D area of the entire wing to include portions "hidden" within fuselage.  This area is used as the nondimensionalization scaling reference for all aerodynamic coefficients.</t>
   </si>
   <si>
     <t xml:space="preserve">Wetted area of wing.  Accounts for all exposed (i.e. air touches it) surfaces of the wing (top and bottom surface must be accounted for). </t>
   </si>
   <si>
-    <t xml:space="preserve">Aspect ratio of the wing.  See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper ratio of the wing (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leading edge sweep of the main wing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep angle of the line connecting the quarter chord of the main wing from root to tip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wing interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the wing and fuselage.  Typical values range from 1.1 (wing that is smoothly integrated/filleted into fuselage) to 1.4 (poorly integrated / filleted wing-fuselage integration).</t>
+    <t>Aspect ratio of the wing.  See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Taper ratio of the wing (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
+    <t>Leading edge sweep of the main wing.</t>
+  </si>
+  <si>
+    <t>Sweep angle of the line connecting the quarter chord of the main wing from root to tip.</t>
+  </si>
+  <si>
+    <t>Wing interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the wing and fuselage.  Typical values range from 1.1 (wing that is smoothly integrated/filleted into fuselage) to 1.4 (poorly integrated / filleted wing-fuselage integration).</t>
   </si>
   <si>
     <t xml:space="preserve">Horizontal stabilizer #1 planform area.  Projected 2-D area of the entire horizontal tail to include portions "hidden" within fuselage. </t>
@@ -352,34 +365,34 @@
     <t xml:space="preserve">Wetted area of horizontal stabilizer #1.  Accounts for all exposed (i.e. air touches it) surfaces (top and bottom surface must be accounted for). </t>
   </si>
   <si>
-    <t xml:space="preserve">Aspect ratio of horizontal stabilizer #1. See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper ratio of the horizontal stabilizer #1 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leading edge sweep of the horizontal stabilizer #1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate of the mean aerodynamic chord of the horizontal stabilizer #1.  Can roughly estimate by taking the average of the root chord and tip chord of the horizontal stabilizer.  Utilized to determine Reynolds number effects for horizontal tail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #1 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the horizontal stabilizer and fuselage (or vertical stabilizer).  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspect ratio of horizontal stabilizer #2. See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper ratio of the horizontal stabilizer #2 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leading edge sweep of the horizontal stabilizer #2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate of the mean aerodynamic chord of the horizontal stabilizer #2.  Can roughly estimate by taking the average of the root chord and tip chord of the horizontal stabilizer.  Utilized to determine Reynolds number effects for horizontal tail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #2 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the horizontal stabilizer and fuselage (or vertical stabilizer).  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
+    <t>Aspect ratio of horizontal stabilizer #1. See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Taper ratio of the horizontal stabilizer #1 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Leading edge sweep of the horizontal stabilizer #1.</t>
+  </si>
+  <si>
+    <t>Estimate of the mean aerodynamic chord of the horizontal stabilizer #1.  Can roughly estimate by taking the average of the root chord and tip chord of the horizontal stabilizer.  Utilized to determine Reynolds number effects for horizontal tail.</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #1 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the horizontal stabilizer and fuselage (or vertical stabilizer).  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
+  </si>
+  <si>
+    <t>Aspect ratio of horizontal stabilizer #2. See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Taper ratio of the horizontal stabilizer #2 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Leading edge sweep of the horizontal stabilizer #2.</t>
+  </si>
+  <si>
+    <t>Estimate of the mean aerodynamic chord of the horizontal stabilizer #2.  Can roughly estimate by taking the average of the root chord and tip chord of the horizontal stabilizer.  Utilized to determine Reynolds number effects for horizontal tail.</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #2 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the horizontal stabilizer and fuselage (or vertical stabilizer).  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
   </si>
   <si>
     <t xml:space="preserve">Vertical stabilizer #1 planform area.  Projected 2-D area of the entire vertical tail to include portions "hidden" within fuselage. </t>
@@ -388,19 +401,19 @@
     <t xml:space="preserve">Wetted area of vertical stabilizer #1.  Accounts for all exposed (i.e. air touches it) surfaces (top and bottom surface must be accounted for). </t>
   </si>
   <si>
-    <t xml:space="preserve">Aspect ratio of vertical stabilizer #1. See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper ratio of the vertical stabilizer #1 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leading edge sweep of the vertical stabilizer #1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate of the mean aerodynamic chord of the vertical stabilizer #1.  Can roughly estimate by taking the average of the root chord and tip chord of the vertical stabilizer.  Utilized to determine Reynolds number effects for vertical tail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #1 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the vertical stabilizer and fuselage.  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
+    <t>Aspect ratio of vertical stabilizer #1. See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Taper ratio of the vertical stabilizer #1 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Leading edge sweep of the vertical stabilizer #1.</t>
+  </si>
+  <si>
+    <t>Estimate of the mean aerodynamic chord of the vertical stabilizer #1.  Can roughly estimate by taking the average of the root chord and tip chord of the vertical stabilizer.  Utilized to determine Reynolds number effects for vertical tail.</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #1 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the vertical stabilizer and fuselage.  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
   </si>
   <si>
     <t xml:space="preserve">Vertical stabilizer #2 planform area.  Projected 2-D area of the entire vertical tail to include portions "hidden" within fuselage. </t>
@@ -409,580 +422,608 @@
     <t xml:space="preserve">Wetted area of vertical stabilizer #2.  Accounts for all exposed (i.e. air touches it) surfaces (top and bottom surface must be accounted for). </t>
   </si>
   <si>
-    <t xml:space="preserve">Aspect ratio of vertical stabilizer #2. See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper ratio of the vertical stabilizer #2 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leading edge sweep of the vertical stabilizer #2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate of the mean aerodynamic chord of the vertical stabilizer #2.  Can roughly estimate by taking the average of the root chord and tip chord of the vertical stabilizer.  Utilized to determine Reynolds number effects for vertical tail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #2 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the vertical stabilizer and fuselage.  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfoil_Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Config</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User defined configuration number label.  Must align with configuration name / row on Main_Input.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfoil_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main wing airfoil name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thick_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main wing airfoil thickness to chord ratio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X_thick_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main wing airfoil location of max thickness in percent chord.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_XXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2D airfoil coefficient of lift data from -5 deg AoA to 15 deg AoA (as denoted by value XXX after the Cl_)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2D airfoil maximum coefficient of lift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_XXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2D airfoil coefficient of drag data from -5 deg AoA to 15 deg AoA (as denoted by value XXX after the Cd_)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum value of airfoil coefficient of drag data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfoil_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #1 airfoil name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thick_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #1 airfoil thickness to chord ratio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X_thick_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #1 airfoil location of max thickness in percent chord.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfoil_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #2 airfoil name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thick_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #2 airfoil thickness to chord ratio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X_thick_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal stabilizer #2 airfoil location of max thickness in percent chord.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfoil_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #1 airfoil name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thick_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #1 airfoil thickness to chord ratio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X_thick_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #1 airfoil location of max thickness in percent chord.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfoil_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #2 airfoil name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thick_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #2 airfoil thickness to chord ratio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X_thick_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical stabilizer #2 airfoil location of max thickness in percent chord.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propulsion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type of propulsion utilized.  Pull down menu w/ limited options:  PROP_Fuel, PROP_Electric, JET_HBP_Turbofan,JET_LBP_Turbofan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of engines / propulsion systems on aircraft.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static sea level uninstalled thrust without afterburner for a jet engine.  If using a prop driven aircraft, set to zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(lb/hr/lb)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thrust specific fuel consupmtion without afterburner for a jet engine. If using a prop driven aircraft, set to zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static sea level uninstalled thrust with afterburner for a jet engine.  If using a prop driven aircraft or jet engine without afterburner, set to zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thrust specific fuel consupmtion with afterburner for a jet engine. If using a prop driven aircraft or a jet engine without afterburner, set to zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installation losses for a jet engine.  Typically 20% = 0.2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaft or brake horsepower of engine driving a prop at sea level.  If using a jet engine, set to zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(lb/hr/hp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specific Fuel Consumption for prop engine.  If using a jet engine, set to zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propellor efficiency.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">altitude_o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M_o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length_f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dia_f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine_f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amax_f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abase_f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swet_f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EWD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sref_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swet_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuarterSweep_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sref-h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swet_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAC_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_h1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sref-h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swet_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAC_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sref-v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swet_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAC_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sref-v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swet_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taper_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAC_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JetSubmersible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jet_Fighter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_neg5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_neg4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_neg3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_neg2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_neg1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_neg5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_neg4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_neg3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_neg2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_neg1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NACA2412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NACA0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PropType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA_mil_sl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFC_mil_sl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA_AB_sl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFC_AB_sl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Install_loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA_shp_sl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFC_sl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prop_eff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prop_Dia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esb_ideal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">install_loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capacity_loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lifetime_loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esb_Real</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eta_b2s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JET_LBP_Turbofan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROP_Fuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROP_Electric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jet_Trainer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JET_HBP_Turbofan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jet_Transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Military_Cargo/Bomber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROP_Turboprop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business_Jet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROP_Turbocharged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAV_Jet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA_Metal_Single</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA_Metal_Twin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA_Composite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homebuilt_Metal/wood_Prop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homebuilt_Composite_Prop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turboprop_Transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sailplane_Unpowered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sailplane_Powered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ag_Aircraft_Prop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aerobatic_Prop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flying_Boat_Prop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAV_Prop</t>
+    <t>Aspect ratio of vertical stabilizer #2. See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Taper ratio of the vertical stabilizer #2 (ratio of root chord to tip chord length). See Wing Geometry reference sheet for equation.</t>
+  </si>
+  <si>
+    <t>Leading edge sweep of the vertical stabilizer #2.</t>
+  </si>
+  <si>
+    <t>Estimate of the mean aerodynamic chord of the vertical stabilizer #2.  Can roughly estimate by taking the average of the root chord and tip chord of the vertical stabilizer.  Utilized to determine Reynolds number effects for vertical tail.</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #2 interference factor.  Accounts for increase in drag due to the complex interaction of the air flow at the junction of the vertical stabilizer and fuselage.  Typical values range from 1.1 (smoothly integrated/filleted) to 1.4 (poorly integrated / filleted integration).</t>
+  </si>
+  <si>
+    <t>Airfoil_Data</t>
+  </si>
+  <si>
+    <t>Config</t>
+  </si>
+  <si>
+    <t>User defined configuration number label.  Must align with configuration name / row on Main_Input.</t>
+  </si>
+  <si>
+    <t>Airfoil_w</t>
+  </si>
+  <si>
+    <t>Main wing airfoil name.</t>
+  </si>
+  <si>
+    <t>Thick_w</t>
+  </si>
+  <si>
+    <t>Main wing airfoil thickness to chord ratio.</t>
+  </si>
+  <si>
+    <t>X_thick_w</t>
+  </si>
+  <si>
+    <t>Main wing airfoil location of max thickness in percent chord.</t>
+  </si>
+  <si>
+    <t>Cl_XXX</t>
+  </si>
+  <si>
+    <t>2D airfoil coefficient of lift data from -5 deg AoA to 15 deg AoA (as denoted by value XXX after the Cl_)</t>
+  </si>
+  <si>
+    <t>Cl_max</t>
+  </si>
+  <si>
+    <t>2D airfoil maximum coefficient of lift</t>
+  </si>
+  <si>
+    <t>Cd_XXX</t>
+  </si>
+  <si>
+    <t>2D airfoil coefficient of drag data from -5 deg AoA to 15 deg AoA (as denoted by value XXX after the Cd_)</t>
+  </si>
+  <si>
+    <t>Cd_min</t>
+  </si>
+  <si>
+    <t>Minimum value of airfoil coefficient of drag data.</t>
+  </si>
+  <si>
+    <t>Airfoil_h1</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #1 airfoil name.</t>
+  </si>
+  <si>
+    <t>Thick_h1</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #1 airfoil thickness to chord ratio.</t>
+  </si>
+  <si>
+    <t>X_thick_h1</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #1 airfoil location of max thickness in percent chord.</t>
+  </si>
+  <si>
+    <t>Airfoil_h2</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #2 airfoil name.</t>
+  </si>
+  <si>
+    <t>Thick_h2</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #2 airfoil thickness to chord ratio.</t>
+  </si>
+  <si>
+    <t>X_thick_h2</t>
+  </si>
+  <si>
+    <t>Horizontal stabilizer #2 airfoil location of max thickness in percent chord.</t>
+  </si>
+  <si>
+    <t>Airfoil_v1</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #1 airfoil name.</t>
+  </si>
+  <si>
+    <t>Thick_v1</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #1 airfoil thickness to chord ratio.</t>
+  </si>
+  <si>
+    <t>X_thick_v1</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #1 airfoil location of max thickness in percent chord.</t>
+  </si>
+  <si>
+    <t>Airfoil_v2</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #2 airfoil name.</t>
+  </si>
+  <si>
+    <t>Thick_v2</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #2 airfoil thickness to chord ratio.</t>
+  </si>
+  <si>
+    <t>X_thick_v2</t>
+  </si>
+  <si>
+    <t>Vertical stabilizer #2 airfoil location of max thickness in percent chord.</t>
+  </si>
+  <si>
+    <t>Propulsion</t>
+  </si>
+  <si>
+    <t>Type of propulsion utilized.  Pull down menu w/ limited options:  PROP_Fuel, PROP_Electric, JET_HBP_Turbofan,JET_LBP_Turbofan</t>
+  </si>
+  <si>
+    <t>Number of engines / propulsion systems on aircraft.</t>
+  </si>
+  <si>
+    <t>lb</t>
+  </si>
+  <si>
+    <t>Static sea level uninstalled thrust without afterburner for a jet engine.  If using a prop driven aircraft, set to zero.</t>
+  </si>
+  <si>
+    <t>(lb/hr/lb)</t>
+  </si>
+  <si>
+    <t>Thrust specific fuel consupmtion without afterburner for a jet engine. If using a prop driven aircraft, set to zero.</t>
+  </si>
+  <si>
+    <t>Static sea level uninstalled thrust with afterburner for a jet engine.  If using a prop driven aircraft or jet engine without afterburner, set to zero.</t>
+  </si>
+  <si>
+    <t>Thrust specific fuel consupmtion with afterburner for a jet engine. If using a prop driven aircraft or a jet engine without afterburner, set to zero.</t>
+  </si>
+  <si>
+    <t>Installation losses for a jet engine.  Typically 20% = 0.2.</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>Shaft or brake horsepower of engine driving a prop at sea level.  If using a jet engine, set to zero.</t>
+  </si>
+  <si>
+    <t>(lb/hr/hp)</t>
+  </si>
+  <si>
+    <t>Specific Fuel Consumption for prop engine.  If using a jet engine, set to zero.</t>
+  </si>
+  <si>
+    <t>Propellor efficiency.</t>
+  </si>
+  <si>
+    <t>ACType</t>
+  </si>
+  <si>
+    <t>altitude_o</t>
+  </si>
+  <si>
+    <t>M_o</t>
+  </si>
+  <si>
+    <t>M_max</t>
+  </si>
+  <si>
+    <t>Length_f</t>
+  </si>
+  <si>
+    <t>Dia_f</t>
+  </si>
+  <si>
+    <t>Fine_f</t>
+  </si>
+  <si>
+    <t>Amax_f</t>
+  </si>
+  <si>
+    <t>Abase_f</t>
+  </si>
+  <si>
+    <t>Swet_f</t>
+  </si>
+  <si>
+    <t>Q_f</t>
+  </si>
+  <si>
+    <t>EWD</t>
+  </si>
+  <si>
+    <t>Sref_w</t>
+  </si>
+  <si>
+    <t>Swet_w</t>
+  </si>
+  <si>
+    <t>AR_w</t>
+  </si>
+  <si>
+    <t>Taper_w</t>
+  </si>
+  <si>
+    <t>Sweep_w</t>
+  </si>
+  <si>
+    <t>QuarterSweep_w</t>
+  </si>
+  <si>
+    <t>Q_w</t>
+  </si>
+  <si>
+    <t>Sref-h1</t>
+  </si>
+  <si>
+    <t>Swet_h1</t>
+  </si>
+  <si>
+    <t>AR_h1</t>
+  </si>
+  <si>
+    <t>Taper_h1</t>
+  </si>
+  <si>
+    <t>Sweep_h1</t>
+  </si>
+  <si>
+    <t>MAC_h1</t>
+  </si>
+  <si>
+    <t>Q_h1</t>
+  </si>
+  <si>
+    <t>Sref-h2</t>
+  </si>
+  <si>
+    <t>Swet_h2</t>
+  </si>
+  <si>
+    <t>AR_h2</t>
+  </si>
+  <si>
+    <t>Taper_h2</t>
+  </si>
+  <si>
+    <t>Sweep_h2</t>
+  </si>
+  <si>
+    <t>MAC_h2</t>
+  </si>
+  <si>
+    <t>Q_h2</t>
+  </si>
+  <si>
+    <t>Sref-v1</t>
+  </si>
+  <si>
+    <t>Swet_v1</t>
+  </si>
+  <si>
+    <t>AR_v1</t>
+  </si>
+  <si>
+    <t>Taper_v1</t>
+  </si>
+  <si>
+    <t>Sweep_v1</t>
+  </si>
+  <si>
+    <t>MAC_v1</t>
+  </si>
+  <si>
+    <t>Q_v1</t>
+  </si>
+  <si>
+    <t>Sref-v2</t>
+  </si>
+  <si>
+    <t>Swet_v2</t>
+  </si>
+  <si>
+    <t>AR_v2</t>
+  </si>
+  <si>
+    <t>Taper_v2</t>
+  </si>
+  <si>
+    <t>Sweep_v2</t>
+  </si>
+  <si>
+    <t>MAC_v2</t>
+  </si>
+  <si>
+    <t>Q_v2</t>
+  </si>
+  <si>
+    <t>Jet_Fighter</t>
+  </si>
+  <si>
+    <t>Cl_neg5</t>
+  </si>
+  <si>
+    <t>Cl_neg4</t>
+  </si>
+  <si>
+    <t>Cl_neg3</t>
+  </si>
+  <si>
+    <t>Cl_neg2</t>
+  </si>
+  <si>
+    <t>Cl_neg1</t>
+  </si>
+  <si>
+    <t>Cl_0</t>
+  </si>
+  <si>
+    <t>Cl_1</t>
+  </si>
+  <si>
+    <t>Cl_2</t>
+  </si>
+  <si>
+    <t>Cl_3</t>
+  </si>
+  <si>
+    <t>Cl_4</t>
+  </si>
+  <si>
+    <t>Cl_5</t>
+  </si>
+  <si>
+    <t>Cl_6</t>
+  </si>
+  <si>
+    <t>Cl_7</t>
+  </si>
+  <si>
+    <t>Cl_8</t>
+  </si>
+  <si>
+    <t>Cl_9</t>
+  </si>
+  <si>
+    <t>Cl_10</t>
+  </si>
+  <si>
+    <t>Cl_11</t>
+  </si>
+  <si>
+    <t>Cl_12</t>
+  </si>
+  <si>
+    <t>Cd_neg5</t>
+  </si>
+  <si>
+    <t>Cd_neg4</t>
+  </si>
+  <si>
+    <t>Cd_neg3</t>
+  </si>
+  <si>
+    <t>Cd_neg2</t>
+  </si>
+  <si>
+    <t>Cd_neg1</t>
+  </si>
+  <si>
+    <t>Cd_0</t>
+  </si>
+  <si>
+    <t>Cd_1</t>
+  </si>
+  <si>
+    <t>Cd_2</t>
+  </si>
+  <si>
+    <t>Cd_3</t>
+  </si>
+  <si>
+    <t>Cd_4</t>
+  </si>
+  <si>
+    <t>Cd_5</t>
+  </si>
+  <si>
+    <t>Cd_6</t>
+  </si>
+  <si>
+    <t>Cd_7</t>
+  </si>
+  <si>
+    <t>Cd_8</t>
+  </si>
+  <si>
+    <t>Cd_9</t>
+  </si>
+  <si>
+    <t>Cd_10</t>
+  </si>
+  <si>
+    <t>Cd_11</t>
+  </si>
+  <si>
+    <t>Cd_12</t>
+  </si>
+  <si>
+    <t>NACA2412</t>
+  </si>
+  <si>
+    <t>NACA0004</t>
+  </si>
+  <si>
+    <t>PropType</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>TA_mil_sl</t>
+  </si>
+  <si>
+    <t>TSFC_mil_sl</t>
+  </si>
+  <si>
+    <t>TA_AB_sl</t>
+  </si>
+  <si>
+    <t>TSFC_AB_sl</t>
+  </si>
+  <si>
+    <t>Install_loss</t>
+  </si>
+  <si>
+    <t>PA_shp_sl</t>
+  </si>
+  <si>
+    <t>SFC_sl</t>
+  </si>
+  <si>
+    <t>Prop_eff</t>
+  </si>
+  <si>
+    <t>Prop_Dia</t>
+  </si>
+  <si>
+    <t>Esb_ideal</t>
+  </si>
+  <si>
+    <t>install_loss</t>
+  </si>
+  <si>
+    <t>capacity_loss</t>
+  </si>
+  <si>
+    <t>lifetime_loss</t>
+  </si>
+  <si>
+    <t>Esb_Real</t>
+  </si>
+  <si>
+    <t>eta_b2s</t>
+  </si>
+  <si>
+    <t>JET_LBP_Turbofan</t>
+  </si>
+  <si>
+    <t>PROP_Fuel</t>
+  </si>
+  <si>
+    <t>PROP_Electric</t>
+  </si>
+  <si>
+    <t>Jet_Trainer</t>
+  </si>
+  <si>
+    <t>JET_HBP_Turbofan</t>
+  </si>
+  <si>
+    <t>Jet_Transport</t>
+  </si>
+  <si>
+    <t>Military_Cargo/Bomber</t>
+  </si>
+  <si>
+    <t>PROP_Turboprop</t>
+  </si>
+  <si>
+    <t>Business_Jet</t>
+  </si>
+  <si>
+    <t>PROP_Turbocharged</t>
+  </si>
+  <si>
+    <t>UAV_Jet</t>
+  </si>
+  <si>
+    <t>GA_Metal_Single</t>
+  </si>
+  <si>
+    <t>GA_Metal_Twin</t>
+  </si>
+  <si>
+    <t>GA_Composite</t>
+  </si>
+  <si>
+    <t>Homebuilt_Metal/wood_Prop</t>
+  </si>
+  <si>
+    <t>Homebuilt_Composite_Prop</t>
+  </si>
+  <si>
+    <t>Turboprop_Transport</t>
+  </si>
+  <si>
+    <t>Sailplane_Unpowered</t>
+  </si>
+  <si>
+    <t>Sailplane_Powered</t>
+  </si>
+  <si>
+    <t>Ag_Aircraft_Prop</t>
+  </si>
+  <si>
+    <t>Aerobatic_Prop</t>
+  </si>
+  <si>
+    <t>Flying_Boat_Prop</t>
+  </si>
+  <si>
+    <t>UAV_Prop</t>
+  </si>
+  <si>
+    <t>NACA0009</t>
+  </si>
+  <si>
+    <t>JetSubmersible_can1.2</t>
+  </si>
+  <si>
+    <t>JetSubmersible_can1.3</t>
+  </si>
+  <si>
+    <t>JetSubmersible_can1.4</t>
+  </si>
+  <si>
+    <t>JetSubmersible_can1.5</t>
+  </si>
+  <si>
+    <t>JetSubmersible_can1.1</t>
+  </si>
+  <si>
+    <t>JetSubmersible_conv1.1</t>
+  </si>
+  <si>
+    <t>JetSubmersible_conv1.2</t>
+  </si>
+  <si>
+    <t>JetSubmersible_conv1.3</t>
+  </si>
+  <si>
+    <t>JetSubmersible_conv1.4</t>
+  </si>
+  <si>
+    <t>JetSubmersible_conv1.5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -991,22 +1032,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1021,7 +1047,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
@@ -1117,184 +1143,112 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="32">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1353,13 +1307,858 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1040" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90782861-53C9-491A-F703-BF46D3377B2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1038" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82E73316-96CE-2233-7E2A-2D6E5030BD58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1036" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55DBCBBD-0327-BB76-069F-E73A29C18A23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1034" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7807232F-34B8-86B9-6218-915B5EBB3645}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1032" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F210585-2C3E-B06D-999A-D027969725E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1030" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FE46B8F-C8AA-90A7-BBE9-05D419A0436F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1028" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79151B1E-DB66-2DBB-2DE0-1458D38EDF4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="_x0000_t202" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{495DDC72-9DD9-56B7-F343-94BDC31A1145}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52EAF356-82AB-0009-C504-795DBE4408B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE91B4DD-0197-A38F-E106-8070E66C3B8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49E10D53-FC5F-45B9-0660-8D260ADCECAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C8B6CCA-6DAF-9FAA-5C34-689C93B14203}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E3C0663-0C61-E9A9-926E-0C2A8C0B8D72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF0A6B61-A278-9BA8-F42B-E1EB187866E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99822206-CF6D-816B-0B6F-3586AF4981BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14497F28-4C4D-3DCF-613A-88DC7F989D97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1375,11 +2174,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Graphic 1" descr=""/>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -1412,11 +2217,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Graphic 3" descr=""/>
+        <xdr:cNvPr id="3" name="Graphic 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -1449,11 +2260,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 4" descr=""/>
+        <xdr:cNvPr id="4" name="Graphic 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -1474,46 +2291,354 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PropType" displayName="PropType" ref="A1:A7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:A7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PropType" displayName="PropType" ref="A1:A7" totalsRowShown="0">
+  <autoFilter ref="A1:A7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="PropType"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PropType"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PropType3" displayName="PropType3" ref="B1:B19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="B1:B19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PropType3" displayName="PropType3" ref="B1:B19" totalsRowShown="0">
+  <autoFilter ref="B1:B19" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="ACType"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ACType"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D82"/>
-  <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="104.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="8.78"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="104.44140625" style="2" customWidth="1"/>
+    <col min="5" max="1025" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1527,12 +2652,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="6" t="e">
-        <f aca="false" t="array" ref="B2:B49">TRANSPOSE([2]Main_Input!A1:AV1)</f>
         <v>#REF!</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1542,7 +2666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1556,7 +2680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" ht="28.8">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
@@ -1570,7 +2694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" ht="28.8">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -1584,7 +2708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +2722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
@@ -1612,7 +2736,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -1626,7 +2750,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
@@ -1640,7 +2764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
         <v>4</v>
       </c>
@@ -1654,7 +2778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" ht="28.8">
       <c r="A11" s="6" t="s">
         <v>4</v>
       </c>
@@ -1668,7 +2792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4">
       <c r="A12" s="6" t="s">
         <v>4</v>
       </c>
@@ -1682,7 +2806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" ht="28.8">
       <c r="A13" s="6" t="s">
         <v>4</v>
       </c>
@@ -1696,7 +2820,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4" ht="28.8">
       <c r="A14" s="6" t="s">
         <v>4</v>
       </c>
@@ -1710,7 +2834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" ht="28.8">
       <c r="A15" s="6" t="s">
         <v>4</v>
       </c>
@@ -1724,7 +2848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4" ht="28.8">
       <c r="A16" s="6" t="s">
         <v>4</v>
       </c>
@@ -1738,7 +2862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
         <v>4</v>
       </c>
@@ -1752,7 +2876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
         <v>4</v>
       </c>
@@ -1766,7 +2890,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
         <v>4</v>
       </c>
@@ -1780,7 +2904,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:4">
       <c r="A20" s="6" t="s">
         <v>4</v>
       </c>
@@ -1794,7 +2918,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:4" ht="43.2">
       <c r="A21" s="6" t="s">
         <v>4</v>
       </c>
@@ -1808,7 +2932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:4" ht="28.5" customHeight="1">
       <c r="A22" s="6" t="s">
         <v>4</v>
       </c>
@@ -1822,7 +2946,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:4" ht="28.8">
       <c r="A23" s="6" t="s">
         <v>4</v>
       </c>
@@ -1836,7 +2960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:4">
       <c r="A24" s="6" t="s">
         <v>4</v>
       </c>
@@ -1850,7 +2974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:4" ht="28.8">
       <c r="A25" s="6" t="s">
         <v>4</v>
       </c>
@@ -1864,7 +2988,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:4">
       <c r="A26" s="6" t="s">
         <v>4</v>
       </c>
@@ -1878,7 +3002,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:4" ht="28.8">
       <c r="A27" s="6" t="s">
         <v>4</v>
       </c>
@@ -1892,7 +3016,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:4" ht="43.2">
       <c r="A28" s="6" t="s">
         <v>4</v>
       </c>
@@ -1906,7 +3030,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:4" ht="28.8">
       <c r="A29" s="6" t="s">
         <v>4</v>
       </c>
@@ -1920,7 +3044,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:4" ht="28.8">
       <c r="A30" s="6" t="s">
         <v>4</v>
       </c>
@@ -1934,7 +3058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:4">
       <c r="A31" s="6" t="s">
         <v>4</v>
       </c>
@@ -1948,7 +3072,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:4" ht="28.8">
       <c r="A32" s="6" t="s">
         <v>4</v>
       </c>
@@ -1962,7 +3086,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:4">
       <c r="A33" s="6" t="s">
         <v>4</v>
       </c>
@@ -1976,7 +3100,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:4" ht="28.8">
       <c r="A34" s="6" t="s">
         <v>4</v>
       </c>
@@ -1990,7 +3114,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:4" ht="43.2">
       <c r="A35" s="6" t="s">
         <v>4</v>
       </c>
@@ -2004,7 +3128,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:4" ht="28.8">
       <c r="A36" s="6" t="s">
         <v>4</v>
       </c>
@@ -2018,7 +3142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:4" ht="28.8">
       <c r="A37" s="6" t="s">
         <v>4</v>
       </c>
@@ -2032,7 +3156,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
         <v>4</v>
       </c>
@@ -2046,7 +3170,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:4" ht="28.8">
       <c r="A39" s="6" t="s">
         <v>4</v>
       </c>
@@ -2060,7 +3184,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
         <v>4</v>
       </c>
@@ -2074,7 +3198,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:4" ht="28.8">
       <c r="A41" s="6" t="s">
         <v>4</v>
       </c>
@@ -2088,7 +3212,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:4" ht="43.2">
       <c r="A42" s="6" t="s">
         <v>4</v>
       </c>
@@ -2102,7 +3226,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:4" ht="28.8">
       <c r="A43" s="6" t="s">
         <v>4</v>
       </c>
@@ -2116,7 +3240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:4" ht="28.8">
       <c r="A44" s="6" t="s">
         <v>4</v>
       </c>
@@ -2130,7 +3254,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:4">
       <c r="A45" s="6" t="s">
         <v>4</v>
       </c>
@@ -2144,7 +3268,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:4" ht="28.8">
       <c r="A46" s="6" t="s">
         <v>4</v>
       </c>
@@ -2158,7 +3282,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:4">
       <c r="A47" s="6" t="s">
         <v>4</v>
       </c>
@@ -2172,7 +3296,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:4" ht="28.8">
       <c r="A48" s="6" t="s">
         <v>4</v>
       </c>
@@ -2186,7 +3310,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:4" ht="43.2">
       <c r="A49" s="6" t="s">
         <v>4</v>
       </c>
@@ -2200,13 +3324,13 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:4">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="10"/>
       <c r="D50" s="11"/>
     </row>
-    <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:4">
       <c r="A51" s="6" t="s">
         <v>55</v>
       </c>
@@ -2220,7 +3344,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:4">
       <c r="A52" s="6" t="s">
         <v>55</v>
       </c>
@@ -2234,7 +3358,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:4">
       <c r="A53" s="6" t="s">
         <v>55</v>
       </c>
@@ -2248,7 +3372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:4">
       <c r="A54" s="6" t="s">
         <v>55</v>
       </c>
@@ -2262,7 +3386,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:4">
       <c r="A55" s="6" t="s">
         <v>55</v>
       </c>
@@ -2276,7 +3400,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:4">
       <c r="A56" s="6" t="s">
         <v>55</v>
       </c>
@@ -2290,7 +3414,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:4">
       <c r="A57" s="6" t="s">
         <v>55</v>
       </c>
@@ -2304,7 +3428,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:4">
       <c r="A58" s="6" t="s">
         <v>55</v>
       </c>
@@ -2318,7 +3442,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:4">
       <c r="A59" s="6" t="s">
         <v>55</v>
       </c>
@@ -2332,7 +3456,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:4">
       <c r="A60" s="6" t="s">
         <v>55</v>
       </c>
@@ -2346,7 +3470,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:4">
       <c r="A61" s="6" t="s">
         <v>55</v>
       </c>
@@ -2360,7 +3484,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:4">
       <c r="A62" s="6" t="s">
         <v>55</v>
       </c>
@@ -2374,7 +3498,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:4">
       <c r="A63" s="6" t="s">
         <v>55</v>
       </c>
@@ -2388,7 +3512,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:4">
       <c r="A64" s="6" t="s">
         <v>55</v>
       </c>
@@ -2402,7 +3526,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:4">
       <c r="A65" s="6" t="s">
         <v>55</v>
       </c>
@@ -2416,7 +3540,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:4">
       <c r="A66" s="6" t="s">
         <v>55</v>
       </c>
@@ -2430,7 +3554,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:4">
       <c r="A67" s="6" t="s">
         <v>55</v>
       </c>
@@ -2444,7 +3568,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:4">
       <c r="A68" s="6" t="s">
         <v>55</v>
       </c>
@@ -2458,7 +3582,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:4">
       <c r="A69" s="6" t="s">
         <v>55</v>
       </c>
@@ -2472,7 +3596,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:4">
       <c r="A70" s="6" t="s">
         <v>55</v>
       </c>
@@ -2486,18 +3610,17 @@
         <v>95</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:4">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="10"/>
       <c r="D71" s="13"/>
     </row>
-    <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:4">
       <c r="A72" s="6" t="s">
         <v>96</v>
       </c>
       <c r="B72" s="6" t="e">
-        <f aca="false" t="array" ref="B72:B82">TRANSPOSE([2]Propulsion!A1:K1)</f>
         <v>#REF!</v>
       </c>
       <c r="C72" s="7" t="s">
@@ -2507,7 +3630,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:4" ht="28.8">
       <c r="A73" s="6" t="s">
         <v>96</v>
       </c>
@@ -2521,7 +3644,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:4">
       <c r="A74" s="6" t="s">
         <v>96</v>
       </c>
@@ -2535,7 +3658,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:4">
       <c r="A75" s="6" t="s">
         <v>96</v>
       </c>
@@ -2549,7 +3672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:4">
       <c r="A76" s="6" t="s">
         <v>96</v>
       </c>
@@ -2563,7 +3686,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:4" ht="28.8">
       <c r="A77" s="6" t="s">
         <v>96</v>
       </c>
@@ -2577,7 +3700,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:4" ht="28.8">
       <c r="A78" s="6" t="s">
         <v>96</v>
       </c>
@@ -2591,7 +3714,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:4">
       <c r="A79" s="6" t="s">
         <v>96</v>
       </c>
@@ -2605,7 +3728,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:4">
       <c r="A80" s="6" t="s">
         <v>96</v>
       </c>
@@ -2619,7 +3742,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:4">
       <c r="A81" s="6" t="s">
         <v>96</v>
       </c>
@@ -2633,7 +3756,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:4">
       <c r="A82" s="6" t="s">
         <v>96</v>
       </c>
@@ -2648,41 +3771,33 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:AV15"/>
-  <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AMK15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="9.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="7" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="7" width="6.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="7" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="7" width="10.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="16.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="7" width="15.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="20" style="7" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="7" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="37" style="7" width="8.78"/>
+    <col min="1" max="1" width="21.21875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="7" customWidth="1"/>
+    <col min="4" max="12" width="8.77734375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="6.77734375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="7" customWidth="1"/>
+    <col min="15" max="15" width="12" style="7" customWidth="1"/>
+    <col min="16" max="16" width="8.77734375" style="7" customWidth="1"/>
+    <col min="17" max="17" width="10.44140625" style="7" customWidth="1"/>
+    <col min="18" max="18" width="16.109375" style="7" customWidth="1"/>
+    <col min="19" max="19" width="15.77734375" style="7" customWidth="1"/>
+    <col min="20" max="35" width="8.77734375" style="7" customWidth="1"/>
+    <col min="36" max="36" width="12" style="7" customWidth="1"/>
+    <col min="37" max="1025" width="8.77734375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:48">
       <c r="A1" s="14" t="s">
         <v>56</v>
       </c>
@@ -2828,201 +3943,1599 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:48">
       <c r="A2" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E2" s="7" t="n">
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="G2" s="7" t="n">
+      <c r="F2" s="7">
+        <v>40</v>
+      </c>
+      <c r="G2" s="7">
         <v>5.5</v>
       </c>
-      <c r="H2" s="7" t="n">
-        <f aca="false">F2/G2</f>
-        <v>7.63636363636364</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <f aca="false">((G2/2)^2)*3.1415</f>
-        <v>23.75759375</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <f aca="false">1.5^2*3.1415</f>
-        <v>7.068375</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>660</v>
-      </c>
-      <c r="L2" s="7" t="n">
+      <c r="H2" s="7">
+        <f>F2/G2</f>
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="I2" s="7">
+        <f>((G2/2)^2)*3.1415+2.5</f>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <f>(F2)*G2*3.1415*0.9</f>
+        <v>622.01700000000005</v>
+      </c>
+      <c r="L2" s="7">
         <v>1</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="7">
         <v>1</v>
       </c>
-      <c r="N2" s="7" t="n">
-        <v>540</v>
-      </c>
-      <c r="O2" s="7" t="n">
-        <f aca="false">N2*2</f>
-        <v>1080</v>
-      </c>
-      <c r="P2" s="7" t="n">
+      <c r="N2" s="7">
+        <v>380</v>
+      </c>
+      <c r="O2" s="7">
+        <f>N2*2</f>
+        <v>760</v>
+      </c>
+      <c r="P2" s="7">
         <v>3.63</v>
       </c>
-      <c r="Q2" s="7" t="n">
+      <c r="Q2" s="7">
         <v>0.2</v>
       </c>
-      <c r="R2" s="7" t="n">
+      <c r="R2" s="7">
+        <v>34</v>
+      </c>
+      <c r="S2" s="7">
+        <f>ATAN(TAN(R2*3.1415/180)-(1-Q2)/(2*(1+Q2)*P2))*180/3.1415</f>
+        <v>30.228351387955257</v>
+      </c>
+      <c r="T2" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U2" s="7">
+        <v>25</v>
+      </c>
+      <c r="V2" s="7">
+        <f>U2*2</f>
+        <v>50</v>
+      </c>
+      <c r="W2" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="X2" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z2" s="7">
+        <f>(2/3)*((2*U2)/((SQRT(W2*U2))*(1+X2)))*(1+X2+X2^2)/(1+X2)</f>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA2" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ2" s="7">
+        <f>2*AI2</f>
+        <v>110</v>
+      </c>
+      <c r="AK2" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="AL2" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM2" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN2" s="7">
+        <f>(2/3)*((2*AI2)/((SQRT(AK2*AI2))*(1+AL2)))*(1+AL2+AL2^2)/(1+AL2)</f>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO2" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48">
+      <c r="A3" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E3" s="7">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7">
         <v>40</v>
       </c>
-      <c r="S2" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="T2" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="U2" s="7" t="n">
+      <c r="G3" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="H3" s="7">
+        <f>F3/G3</f>
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="I3" s="7">
+        <f>((G3/2)^2)*3.1415+2.5</f>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7">
+        <f>(F3)*G3*3.1415*0.9</f>
+        <v>622.01700000000005</v>
+      </c>
+      <c r="L3" s="7">
+        <v>1</v>
+      </c>
+      <c r="M3" s="7">
+        <v>1</v>
+      </c>
+      <c r="N3" s="7">
+        <v>360</v>
+      </c>
+      <c r="O3" s="7">
+        <f>N3*2</f>
+        <v>720</v>
+      </c>
+      <c r="P3" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R3" s="7">
+        <v>48.2</v>
+      </c>
+      <c r="S3" s="7">
+        <f>ATAN(TAN(R3*3.1415/180)-(1-Q3)/(2*(1+Q3)*P3))*180/3.1415</f>
+        <v>44.036243565531883</v>
+      </c>
+      <c r="T3" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U3" s="7">
         <v>25</v>
       </c>
-      <c r="V2" s="7" t="n">
-        <f aca="false">U2*2</f>
+      <c r="V3" s="7">
+        <f>U3*2</f>
         <v>50</v>
       </c>
-      <c r="W2" s="7" t="n">
+      <c r="W3" s="7">
         <v>2.8</v>
       </c>
-      <c r="X2" s="7" t="n">
+      <c r="X3" s="7">
         <v>0.4</v>
       </c>
-      <c r="Y2" s="7" t="n">
+      <c r="Y3" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z3" s="7">
+        <f>(2/3)*((2*U3)/((SQRT(W3*U3))*(1+X3)))*(1+X3+X3^2)/(1+X3)</f>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA3" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ3" s="7">
+        <f>2*AI3</f>
+        <v>110</v>
+      </c>
+      <c r="AK3" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="AL3" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM3" s="7">
         <v>20</v>
       </c>
-      <c r="Z2" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA2" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ2" s="7" t="n">
-        <f aca="false">2*AI2</f>
-        <v>150</v>
-      </c>
-      <c r="AK2" s="7" t="n">
+      <c r="AN3" s="7">
+        <f>(2/3)*((2*AI3)/((SQRT(AK3*AI3))*(1+AL3)))*(1+AL3+AL3^2)/(1+AL3)</f>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO3" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48">
+      <c r="A4" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7">
+        <v>40</v>
+      </c>
+      <c r="G4" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="H4" s="7">
+        <f>F4/G4</f>
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="I4" s="7">
+        <f>((G4/2)^2)*3.1415+2.5</f>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <f>(F4)*G4*3.1415*0.9</f>
+        <v>622.01700000000005</v>
+      </c>
+      <c r="L4" s="7">
+        <v>1</v>
+      </c>
+      <c r="M4" s="7">
+        <v>1</v>
+      </c>
+      <c r="N4" s="7">
+        <v>360</v>
+      </c>
+      <c r="O4" s="7">
+        <f>N4*2</f>
+        <v>720</v>
+      </c>
+      <c r="P4" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R4" s="7">
+        <v>48.2</v>
+      </c>
+      <c r="S4" s="7">
+        <f>ATAN(TAN(R4*3.1415/180)-(1-Q4)/(2*(1+Q4)*P4))*180/3.1415</f>
+        <v>44.036243565531883</v>
+      </c>
+      <c r="T4" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U4" s="7">
+        <v>25</v>
+      </c>
+      <c r="V4" s="7">
+        <f>U4*2</f>
+        <v>50</v>
+      </c>
+      <c r="W4" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="X4" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z4" s="7">
+        <f>(2/3)*((2*U4)/((SQRT(W4*U4))*(1+X4)))*(1+X4+X4^2)/(1+X4)</f>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ4" s="7">
+        <f>2*AI4</f>
+        <v>110</v>
+      </c>
+      <c r="AK4" s="7">
         <v>1.3</v>
       </c>
-      <c r="AL2" s="7" t="n">
+      <c r="AL4" s="7">
         <v>0.4</v>
       </c>
-      <c r="AM2" s="7" t="n">
+      <c r="AM4" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN4" s="7">
+        <f>(2/3)*((2*AI4)/((SQRT(AK4*AI4))*(1+AL4)))*(1+AL4+AL4^2)/(1+AL4)</f>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO4" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48">
+      <c r="A5" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
         <v>40</v>
       </c>
-      <c r="AN2" s="7" t="n">
-        <f aca="false">(2/3)*((2*AI2)/((SQRT(AK2*AI2))*(1+AL2)))*(1+AL2+AL2^2)/(1+AL2)</f>
-        <v>8.06057863597204</v>
-      </c>
-      <c r="AO2" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AP2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="20" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="G5" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="H5" s="7">
+        <f>F5/G5</f>
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="I5" s="7">
+        <f>((G5/2)^2)*3.1415+2.5</f>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <f>(F5)*G5*3.1415*0.9</f>
+        <v>622.01700000000005</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7">
+        <v>1</v>
+      </c>
+      <c r="N5" s="7">
+        <v>360</v>
+      </c>
+      <c r="O5" s="7">
+        <f>N5*2</f>
+        <v>720</v>
+      </c>
+      <c r="P5" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R5" s="7">
+        <v>48.2</v>
+      </c>
+      <c r="S5" s="7">
+        <f>ATAN(TAN(R5*3.1415/180)-(1-Q5)/(2*(1+Q5)*P5))*180/3.1415</f>
+        <v>44.036243565531883</v>
+      </c>
+      <c r="T5" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U5" s="7">
+        <v>25</v>
+      </c>
+      <c r="V5" s="7">
+        <f>U5*2</f>
+        <v>50</v>
+      </c>
+      <c r="W5" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="X5" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z5" s="7">
+        <f>(2/3)*((2*U5)/((SQRT(W5*U5))*(1+X5)))*(1+X5+X5^2)/(1+X5)</f>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA5" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ5" s="7">
+        <f>2*AI5</f>
+        <v>110</v>
+      </c>
+      <c r="AK5" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="AL5" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM5" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN5" s="7">
+        <f>(2/3)*((2*AI5)/((SQRT(AK5*AI5))*(1+AL5)))*(1+AL5+AL5^2)/(1+AL5)</f>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO5" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48">
+      <c r="A6" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>40</v>
+      </c>
+      <c r="G6" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="7">
+        <f>F6/G6</f>
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="I6" s="7">
+        <f>((G6/2)^2)*3.1415+2.5</f>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <f>(F6)*G6*3.1415*0.9</f>
+        <v>622.01700000000005</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1</v>
+      </c>
+      <c r="M6" s="7">
+        <v>1</v>
+      </c>
+      <c r="N6" s="7">
+        <v>360</v>
+      </c>
+      <c r="O6" s="7">
+        <f>N6*2</f>
+        <v>720</v>
+      </c>
+      <c r="P6" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R6" s="7">
+        <v>48.2</v>
+      </c>
+      <c r="S6" s="7">
+        <f>ATAN(TAN(R6*3.1415/180)-(1-Q6)/(2*(1+Q6)*P6))*180/3.1415</f>
+        <v>44.036243565531883</v>
+      </c>
+      <c r="T6" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U6" s="7">
+        <v>25</v>
+      </c>
+      <c r="V6" s="7">
+        <f>U6*2</f>
+        <v>50</v>
+      </c>
+      <c r="W6" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="X6" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z6" s="7">
+        <f>(2/3)*((2*U6)/((SQRT(W6*U6))*(1+X6)))*(1+X6+X6^2)/(1+X6)</f>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ6" s="7">
+        <f>2*AI6</f>
+        <v>110</v>
+      </c>
+      <c r="AK6" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="AL6" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM6" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN6" s="7">
+        <f>(2/3)*((2*AI6)/((SQRT(AK6*AI6))*(1+AL6)))*(1+AL6+AL6^2)/(1+AL6)</f>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO6" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48">
+      <c r="A7" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <v>25</v>
+      </c>
+      <c r="G7" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="7">
+        <f>F7/G7</f>
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="I7" s="7">
+        <f>((G7/2)^2)*3.1415+2.5</f>
+        <v>18.40384375</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <f>F7*G7*3.1415*0.93</f>
+        <v>328.67943750000006</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7">
+        <v>310</v>
+      </c>
+      <c r="O7" s="7">
+        <f>N7*2</f>
+        <v>620</v>
+      </c>
+      <c r="P7" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="R7" s="7">
+        <v>44</v>
+      </c>
+      <c r="S7" s="7">
+        <f>ATAN(TAN(R7*3.1415/180)-(1-Q7)/(2*(1+Q7)*P7))*180/3.1415</f>
+        <v>40.208174924683249</v>
+      </c>
+      <c r="T7" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U7" s="7">
+        <v>10</v>
+      </c>
+      <c r="V7" s="7">
+        <f>U7*2</f>
+        <v>20</v>
+      </c>
+      <c r="W7" s="7">
+        <v>5</v>
+      </c>
+      <c r="X7" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>31</v>
+      </c>
+      <c r="Z7" s="7">
+        <f>(2/3)*((2*U7)/((SQRT(W7*U7))*(1+X7)))*(1+X7+X7^2)/(1+X7)</f>
+        <v>1.6237266827246648</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="7">
+        <v>17</v>
+      </c>
+      <c r="AJ7" s="7">
+        <f>2*AI7</f>
+        <v>34</v>
+      </c>
+      <c r="AK7" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="AL7" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM7" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN7" s="7">
+        <f>(2/3)*((2*AI7)/((SQRT(AK7*AI7))*(1+AL7)))*(1+AL7+AL7^2)/(1+AL7)</f>
+        <v>3.2613354542804762</v>
+      </c>
+      <c r="AO7" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48">
+      <c r="A8" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
+        <v>25</v>
+      </c>
+      <c r="G8" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="H8" s="7">
+        <f>F8/G8</f>
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="I8" s="7">
+        <f>((G8/2)^2)*3.1415+2.5</f>
+        <v>18.40384375</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <f>F8*G8*3.1415*0.93</f>
+        <v>328.67943750000006</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1</v>
+      </c>
+      <c r="M8" s="7">
+        <v>1</v>
+      </c>
+      <c r="N8" s="7">
+        <v>310</v>
+      </c>
+      <c r="O8" s="7">
+        <f>N8*2</f>
+        <v>620</v>
+      </c>
+      <c r="P8" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="R8" s="7">
+        <v>44</v>
+      </c>
+      <c r="S8" s="7">
+        <f>ATAN(TAN(R8*3.1415/180)-(1-Q8)/(2*(1+Q8)*P8))*180/3.1415</f>
+        <v>40.208174924683249</v>
+      </c>
+      <c r="T8" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U8" s="7">
+        <v>10</v>
+      </c>
+      <c r="V8" s="7">
+        <f>U8*2</f>
+        <v>20</v>
+      </c>
+      <c r="W8" s="7">
+        <v>5</v>
+      </c>
+      <c r="X8" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>31</v>
+      </c>
+      <c r="Z8" s="7">
+        <f>(2/3)*((2*U8)/((SQRT(W8*U8))*(1+X8)))*(1+X8+X8^2)/(1+X8)</f>
+        <v>1.6237266827246648</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="7">
+        <v>17</v>
+      </c>
+      <c r="AJ8" s="7">
+        <f>2*AI8</f>
+        <v>34</v>
+      </c>
+      <c r="AK8" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="AL8" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM8" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN8" s="7">
+        <f>(2/3)*((2*AI8)/((SQRT(AK8*AI8))*(1+AL8)))*(1+AL8+AL8^2)/(1+AL8)</f>
+        <v>3.2613354542804762</v>
+      </c>
+      <c r="AO8" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48">
+      <c r="A9" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7">
+        <v>25</v>
+      </c>
+      <c r="G9" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="7">
+        <f>F9/G9</f>
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="I9" s="7">
+        <f>((G9/2)^2)*3.1415+2.5</f>
+        <v>18.40384375</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <f>F9*G9*3.1415*0.93</f>
+        <v>328.67943750000006</v>
+      </c>
+      <c r="L9" s="7">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7">
+        <v>310</v>
+      </c>
+      <c r="O9" s="7">
+        <f>N9*2</f>
+        <v>620</v>
+      </c>
+      <c r="P9" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="R9" s="7">
+        <v>44</v>
+      </c>
+      <c r="S9" s="7">
+        <f>ATAN(TAN(R9*3.1415/180)-(1-Q9)/(2*(1+Q9)*P9))*180/3.1415</f>
+        <v>40.208174924683249</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U9" s="7">
+        <v>10</v>
+      </c>
+      <c r="V9" s="7">
+        <f>U9*2</f>
+        <v>20</v>
+      </c>
+      <c r="W9" s="7">
+        <v>5</v>
+      </c>
+      <c r="X9" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>31</v>
+      </c>
+      <c r="Z9" s="7">
+        <f>(2/3)*((2*U9)/((SQRT(W9*U9))*(1+X9)))*(1+X9+X9^2)/(1+X9)</f>
+        <v>1.6237266827246648</v>
+      </c>
+      <c r="AA9" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="7">
+        <v>17</v>
+      </c>
+      <c r="AJ9" s="7">
+        <f>2*AI9</f>
+        <v>34</v>
+      </c>
+      <c r="AK9" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="AL9" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM9" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN9" s="7">
+        <f>(2/3)*((2*AI9)/((SQRT(AK9*AI9))*(1+AL9)))*(1+AL9+AL9^2)/(1+AL9)</f>
+        <v>3.2613354542804762</v>
+      </c>
+      <c r="AO9" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48">
+      <c r="A10" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7">
+        <v>25</v>
+      </c>
+      <c r="G10" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="H10" s="7">
+        <f>F10/G10</f>
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="I10" s="7">
+        <f>((G10/2)^2)*3.1415+2.5</f>
+        <v>18.40384375</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <f>F10*G10*3.1415*0.93</f>
+        <v>328.67943750000006</v>
+      </c>
+      <c r="L10" s="7">
+        <v>1</v>
+      </c>
+      <c r="M10" s="7">
+        <v>1</v>
+      </c>
+      <c r="N10" s="7">
+        <v>310</v>
+      </c>
+      <c r="O10" s="7">
+        <f>N10*2</f>
+        <v>620</v>
+      </c>
+      <c r="P10" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="R10" s="7">
+        <v>44</v>
+      </c>
+      <c r="S10" s="7">
+        <f>ATAN(TAN(R10*3.1415/180)-(1-Q10)/(2*(1+Q10)*P10))*180/3.1415</f>
+        <v>40.208174924683249</v>
+      </c>
+      <c r="T10" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U10" s="7">
+        <v>10</v>
+      </c>
+      <c r="V10" s="7">
+        <f>U10*2</f>
+        <v>20</v>
+      </c>
+      <c r="W10" s="7">
+        <v>5</v>
+      </c>
+      <c r="X10" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="Y10" s="7">
+        <v>31</v>
+      </c>
+      <c r="Z10" s="7">
+        <f>(2/3)*((2*U10)/((SQRT(W10*U10))*(1+X10)))*(1+X10+X10^2)/(1+X10)</f>
+        <v>1.6237266827246648</v>
+      </c>
+      <c r="AA10" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="7">
+        <v>17</v>
+      </c>
+      <c r="AJ10" s="7">
+        <f>2*AI10</f>
+        <v>34</v>
+      </c>
+      <c r="AK10" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="AL10" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM10" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN10" s="7">
+        <f>(2/3)*((2*AI10)/((SQRT(AK10*AI10))*(1+AL10)))*(1+AL10+AL10^2)/(1+AL10)</f>
+        <v>3.2613354542804762</v>
+      </c>
+      <c r="AO10" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48">
+      <c r="A11" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7">
+        <v>25</v>
+      </c>
+      <c r="G11" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="7">
+        <f>F11/G11</f>
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="I11" s="7">
+        <f>((G11/2)^2)*3.1415+2.5</f>
+        <v>18.40384375</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7">
+        <f>F11*G11*3.1415*0.93</f>
+        <v>328.67943750000006</v>
+      </c>
+      <c r="L11" s="7">
+        <v>1</v>
+      </c>
+      <c r="M11" s="7">
+        <v>1</v>
+      </c>
+      <c r="N11" s="7">
+        <v>310</v>
+      </c>
+      <c r="O11" s="7">
+        <f>N11*2</f>
+        <v>620</v>
+      </c>
+      <c r="P11" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="R11" s="7">
+        <v>44</v>
+      </c>
+      <c r="S11" s="7">
+        <f>ATAN(TAN(R11*3.1415/180)-(1-Q11)/(2*(1+Q11)*P11))*180/3.1415</f>
+        <v>40.208174924683249</v>
+      </c>
+      <c r="T11" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U11" s="7">
+        <v>10</v>
+      </c>
+      <c r="V11" s="7">
+        <f>U11*2</f>
+        <v>20</v>
+      </c>
+      <c r="W11" s="7">
+        <v>5</v>
+      </c>
+      <c r="X11" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="Y11" s="7">
+        <v>31</v>
+      </c>
+      <c r="Z11" s="7">
+        <f>(2/3)*((2*U11)/((SQRT(W11*U11))*(1+X11)))*(1+X11+X11^2)/(1+X11)</f>
+        <v>1.6237266827246648</v>
+      </c>
+      <c r="AA11" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="7">
+        <v>17</v>
+      </c>
+      <c r="AJ11" s="7">
+        <f>2*AI11</f>
+        <v>34</v>
+      </c>
+      <c r="AK11" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="AL11" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM11" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN11" s="7">
+        <f>(2/3)*((2*AI11)/((SQRT(AK11*AI11))*(1+AL11)))*(1+AL11+AL11^2)/(1+AL11)</f>
+        <v>3.2613354542804762</v>
+      </c>
+      <c r="AO11" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" s="20" customFormat="1"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B14" type="list">
-      <formula1>Lists!$B$2:$B$19</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>Lists!$B$2:$B$19</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>B2:B14</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:BB16"/>
-  <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AMK19"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="21" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="21" width="11.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="3" style="21" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="21" width="11.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="21" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="21" width="9.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="21" width="11.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="21" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="21" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="21" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="21" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="21" width="11.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="53" style="21" width="8.78"/>
+    <col min="1" max="1" width="21.21875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" style="21" customWidth="1"/>
+    <col min="3" max="42" width="8.77734375" style="21" customWidth="1"/>
+    <col min="43" max="43" width="11.77734375" style="21" customWidth="1"/>
+    <col min="44" max="44" width="8.77734375" style="21" customWidth="1"/>
+    <col min="45" max="45" width="9.77734375" style="21" customWidth="1"/>
+    <col min="46" max="46" width="11.77734375" style="21" customWidth="1"/>
+    <col min="47" max="47" width="8.77734375" style="21" customWidth="1"/>
+    <col min="48" max="49" width="10.33203125" style="21" customWidth="1"/>
+    <col min="50" max="50" width="8.77734375" style="21" customWidth="1"/>
+    <col min="51" max="51" width="10.33203125" style="21" customWidth="1"/>
+    <col min="52" max="52" width="11.77734375" style="21" customWidth="1"/>
+    <col min="53" max="1025" width="8.77734375" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:54">
       <c r="A1" s="22" t="s">
         <v>56</v>
       </c>
@@ -3036,115 +5549,115 @@
         <v>62</v>
       </c>
       <c r="E1" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="N1" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="Q1" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="R1" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="S1" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="T1" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="U1" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="U1" s="22" t="s">
+      <c r="V1" s="22" t="s">
         <v>176</v>
-      </c>
-      <c r="V1" s="22" t="s">
-        <v>177</v>
       </c>
       <c r="W1" s="22" t="s">
         <v>66</v>
       </c>
       <c r="X1" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y1" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="AA1" s="22" t="s">
+      <c r="AB1" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="AB1" s="22" t="s">
+      <c r="AC1" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="AC1" s="22" t="s">
+      <c r="AD1" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="AD1" s="22" t="s">
+      <c r="AE1" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="AE1" s="22" t="s">
+      <c r="AF1" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="AF1" s="22" t="s">
+      <c r="AG1" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="AG1" s="22" t="s">
+      <c r="AH1" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="AH1" s="22" t="s">
+      <c r="AI1" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="AI1" s="22" t="s">
+      <c r="AJ1" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="AJ1" s="22" t="s">
+      <c r="AK1" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="AK1" s="22" t="s">
+      <c r="AL1" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="AL1" s="22" t="s">
+      <c r="AM1" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="AM1" s="22" t="s">
+      <c r="AN1" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="AN1" s="22" t="s">
+      <c r="AO1" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="AO1" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="AP1" s="22" t="s">
         <v>70</v>
@@ -3186,513 +5699,2640 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>158</v>
+    <row r="2" spans="1:54">
+      <c r="A2" s="21" t="str">
+        <f>Main_Input!A2</f>
+        <v>JetSubmersible_can1.1</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D2" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F2" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G2" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H2" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I2" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J2" s="21">
+        <v>0</v>
+      </c>
+      <c r="K2" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L2" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M2" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N2" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O2" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P2" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q2" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R2" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S2" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T2" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U2" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V2" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W2" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X2" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y2" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z2" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA2" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB2" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC2" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD2" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE2" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF2" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG2" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH2" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI2" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ2" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK2" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL2" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM2" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN2" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO2" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP2" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ2" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="21" t="n">
+      <c r="AR2" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS2" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT2" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX2" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY2" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ2" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54">
+      <c r="A3" s="21" t="str">
+        <f>Main_Input!A3</f>
+        <v>JetSubmersible_can1.2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D3" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E3" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F3" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G3" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H3" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I3" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J3" s="21">
+        <v>0</v>
+      </c>
+      <c r="K3" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L3" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M3" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N3" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O3" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P3" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q3" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R3" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S3" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T3" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U3" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V3" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W3" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X3" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y3" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z3" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA3" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB3" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC3" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD3" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE3" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF3" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG3" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH3" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI3" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ3" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK3" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL3" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM3" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN3" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO3" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP3" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ3" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR3" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS3" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT3" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX3" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY3" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ3" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54">
+      <c r="A4" s="21" t="str">
+        <f>Main_Input!A4</f>
+        <v>JetSubmersible_can1.3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D4" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F4" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G4" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H4" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I4" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J4" s="21">
+        <v>0</v>
+      </c>
+      <c r="K4" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L4" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M4" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N4" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O4" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P4" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q4" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R4" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S4" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T4" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U4" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V4" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W4" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X4" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y4" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z4" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA4" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB4" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC4" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD4" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE4" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF4" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG4" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH4" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI4" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ4" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK4" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL4" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM4" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN4" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO4" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP4" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ4" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR4" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS4" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT4" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX4" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY4" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ4" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54">
+      <c r="A5" s="21" t="str">
+        <f>Main_Input!A5</f>
+        <v>JetSubmersible_can1.4</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D5" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F5" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G5" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H5" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I5" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J5" s="21">
+        <v>0</v>
+      </c>
+      <c r="K5" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L5" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M5" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N5" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O5" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P5" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q5" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R5" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S5" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T5" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U5" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V5" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W5" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X5" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y5" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z5" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA5" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB5" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC5" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD5" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE5" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF5" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG5" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH5" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI5" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ5" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK5" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL5" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM5" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN5" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO5" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP5" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR5" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS5" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX5" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY5" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ5" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54">
+      <c r="A6" s="21" t="str">
+        <f>Main_Input!A6</f>
+        <v>JetSubmersible_can1.5</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D6" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F6" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G6" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H6" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I6" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J6" s="21">
+        <v>0</v>
+      </c>
+      <c r="K6" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L6" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M6" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N6" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O6" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P6" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q6" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R6" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S6" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T6" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U6" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V6" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W6" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X6" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y6" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z6" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA6" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB6" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC6" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD6" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE6" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF6" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG6" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH6" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI6" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ6" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK6" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL6" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM6" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN6" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO6" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP6" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ6" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR6" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS6" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT6" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX6" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY6" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ6" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:54">
+      <c r="A7" s="21" t="str">
+        <f>Main_Input!A7</f>
+        <v>JetSubmersible_conv1.1</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D7" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F7" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G7" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H7" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I7" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J7" s="21">
+        <v>0</v>
+      </c>
+      <c r="K7" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L7" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M7" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N7" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O7" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P7" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q7" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R7" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S7" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T7" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U7" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V7" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W7" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X7" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y7" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z7" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA7" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB7" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC7" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD7" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE7" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF7" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG7" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH7" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI7" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ7" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK7" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL7" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM7" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN7" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO7" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP7" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ7" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR7" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS7" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX7" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY7" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ7" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54">
+      <c r="A8" s="21" t="str">
+        <f>Main_Input!A8</f>
+        <v>JetSubmersible_conv1.2</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D8" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F8" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G8" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H8" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I8" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J8" s="21">
+        <v>0</v>
+      </c>
+      <c r="K8" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L8" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M8" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N8" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O8" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P8" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q8" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R8" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S8" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T8" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U8" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V8" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W8" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X8" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y8" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z8" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA8" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB8" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC8" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD8" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE8" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF8" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG8" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH8" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI8" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ8" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK8" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL8" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM8" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN8" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO8" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP8" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ8" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR8" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS8" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX8" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY8" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ8" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54">
+      <c r="A9" s="21" t="str">
+        <f>Main_Input!A9</f>
+        <v>JetSubmersible_conv1.3</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D9" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F9" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G9" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H9" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I9" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J9" s="21">
+        <v>0</v>
+      </c>
+      <c r="K9" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L9" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M9" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N9" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O9" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P9" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q9" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R9" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S9" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T9" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U9" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V9" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W9" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X9" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y9" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z9" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA9" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB9" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC9" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD9" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE9" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF9" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG9" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH9" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI9" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ9" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK9" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL9" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM9" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN9" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO9" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP9" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ9" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR9" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS9" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX9" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY9" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ9" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54">
+      <c r="A10" s="21" t="str">
+        <f>Main_Input!A10</f>
+        <v>JetSubmersible_conv1.4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D10" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F10" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G10" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H10" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I10" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J10" s="21">
+        <v>0</v>
+      </c>
+      <c r="K10" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L10" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M10" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N10" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O10" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P10" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q10" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R10" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S10" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T10" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U10" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V10" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W10" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X10" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y10" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z10" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA10" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB10" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC10" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD10" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE10" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF10" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG10" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH10" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI10" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ10" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK10" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL10" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM10" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN10" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO10" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP10" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ10" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR10" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS10" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT10" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX10" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY10" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ10" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54">
+      <c r="A11" s="21" t="str">
+        <f>Main_Input!A11</f>
+        <v>JetSubmersible_conv1.5</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="D11" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.56269999999999998</v>
+      </c>
+      <c r="F11" s="21">
+        <v>-0.43840000000000001</v>
+      </c>
+      <c r="G11" s="21">
+        <v>-0.30609999999999998</v>
+      </c>
+      <c r="H11" s="21">
+        <v>-0.18940000000000001</v>
+      </c>
+      <c r="I11" s="21">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="J11" s="21">
+        <v>0</v>
+      </c>
+      <c r="K11" s="21">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L11" s="21">
+        <v>0.1893</v>
+      </c>
+      <c r="M11" s="21">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N11" s="21">
+        <v>0.4385</v>
+      </c>
+      <c r="O11" s="21">
+        <v>0.56289999999999996</v>
+      </c>
+      <c r="P11" s="21">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>0.81320000000000003</v>
+      </c>
+      <c r="R11" s="21">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="S11" s="21">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="T11" s="21">
+        <v>1.0682</v>
+      </c>
+      <c r="U11" s="21">
+        <v>1.1442000000000001</v>
+      </c>
+      <c r="V11" s="21">
+        <v>1.2101999999999999</v>
+      </c>
+      <c r="W11" s="21">
+        <v>1.2837000000000001</v>
+      </c>
+      <c r="X11" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="Y11" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="Z11" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AA11" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AB11" s="21">
+        <v>5.8700000000000002E-3</v>
+      </c>
+      <c r="AC11" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AD11" s="21">
+        <v>5.8799999999999998E-3</v>
+      </c>
+      <c r="AE11" s="21">
+        <v>6.2700000000000004E-3</v>
+      </c>
+      <c r="AF11" s="21">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="AG11" s="21">
+        <v>8.1200000000000005E-3</v>
+      </c>
+      <c r="AH11" s="21">
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AI11" s="21">
+        <v>9.8899999999999995E-3</v>
+      </c>
+      <c r="AJ11" s="21">
+        <v>1.089E-2</v>
+      </c>
+      <c r="AK11" s="21">
+        <v>1.209E-2</v>
+      </c>
+      <c r="AL11" s="21">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="AM11" s="21">
+        <v>1.5679999999999999E-2</v>
+      </c>
+      <c r="AN11" s="21">
+        <v>1.7940000000000001E-2</v>
+      </c>
+      <c r="AO11" s="21">
+        <v>2.0990000000000002E-2</v>
+      </c>
+      <c r="AP11" s="21">
+        <v>5.7299999999999999E-3</v>
+      </c>
+      <c r="AQ11" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR11" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AS11" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AT11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX11" s="21">
+        <v>0.04</v>
+      </c>
+      <c r="AY11" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="AZ11" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:54" s="25" customFormat="1"/>
+    <row r="19" spans="2:54">
+      <c r="B19" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" s="21">
         <v>0.12</v>
       </c>
-      <c r="D2" s="21" t="n">
+      <c r="D19" s="21">
         <v>0.3</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <f aca="false">-0.483</f>
-        <v>-0.483</v>
-      </c>
-      <c r="F2" s="23" t="n">
-        <f aca="false">-0.3983</f>
-        <v>-0.3983</v>
-      </c>
-      <c r="G2" s="23" t="n">
-        <f aca="false">-0.3108</f>
-        <v>-0.3108</v>
-      </c>
-      <c r="H2" s="23" t="n">
+      <c r="E19" s="6">
+        <f>-0.483</f>
+        <v>-0.48299999999999998</v>
+      </c>
+      <c r="F19" s="23">
+        <f>-0.3983</f>
+        <v>-0.39829999999999999</v>
+      </c>
+      <c r="G19" s="23">
+        <f>-0.3108</f>
+        <v>-0.31080000000000002</v>
+      </c>
+      <c r="H19" s="23">
         <v>-0.2485</v>
       </c>
-      <c r="I2" s="23" t="n">
+      <c r="I19" s="23">
         <v>-0.1244</v>
       </c>
-      <c r="J2" s="21" t="n">
-        <v>-0.0589</v>
-      </c>
-      <c r="K2" s="23" t="n">
-        <v>0.1375</v>
-      </c>
-      <c r="L2" s="23" t="n">
-        <v>0.3025</v>
-      </c>
-      <c r="M2" s="23" t="n">
-        <v>0.4528</v>
-      </c>
-      <c r="N2" s="23" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="O2" s="23" t="n">
+      <c r="J19" s="21">
+        <v>-5.8900000000000001E-2</v>
+      </c>
+      <c r="K19" s="23">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="L19" s="23">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="M19" s="23">
+        <v>0.45279999999999998</v>
+      </c>
+      <c r="N19" s="23">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="O19" s="23">
         <v>0.7429</v>
       </c>
-      <c r="P2" s="23" t="n">
-        <v>0.8567</v>
-      </c>
-      <c r="Q2" s="23" t="n">
-        <v>0.9598</v>
-      </c>
-      <c r="R2" s="21" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="S2" s="21" t="n">
+      <c r="P19" s="23">
+        <v>0.85670000000000002</v>
+      </c>
+      <c r="Q19" s="23">
+        <v>0.95979999999999999</v>
+      </c>
+      <c r="R19" s="21">
+        <v>1.0251999999999999</v>
+      </c>
+      <c r="S19" s="21">
         <v>1.0969</v>
       </c>
-      <c r="T2" s="23" t="n">
+      <c r="T19" s="23">
         <v>1.1591</v>
       </c>
-      <c r="U2" s="23" t="n">
+      <c r="U19" s="23">
         <v>1.1391</v>
       </c>
-      <c r="V2" s="21" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="W2" s="21" t="n">
-        <f aca="false">1.1591</f>
+      <c r="V19" s="21">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="W19" s="21">
+        <f>1.1591</f>
         <v>1.1591</v>
       </c>
-      <c r="X2" s="23" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="Y2" s="23" t="n">
-        <v>0.02669</v>
-      </c>
-      <c r="Z2" s="23" t="n">
-        <v>0.02669</v>
-      </c>
-      <c r="AA2" s="23" t="n">
-        <v>0.02133</v>
-      </c>
-      <c r="AB2" s="23" t="n">
-        <v>0.02191</v>
-      </c>
-      <c r="AC2" s="23" t="n">
-        <v>0.02406</v>
-      </c>
-      <c r="AD2" s="23" t="n">
-        <v>0.0281</v>
-      </c>
-      <c r="AE2" s="23" t="n">
-        <v>0.03099</v>
-      </c>
-      <c r="AF2" s="23" t="n">
-        <v>0.03304</v>
-      </c>
-      <c r="AG2" s="23" t="n">
-        <v>0.03375</v>
-      </c>
-      <c r="AH2" s="23" t="n">
-        <v>0.03256</v>
-      </c>
-      <c r="AI2" s="23" t="n">
-        <v>0.03159</v>
-      </c>
-      <c r="AJ2" s="23" t="n">
-        <v>0.03027</v>
-      </c>
-      <c r="AK2" s="24" t="n">
-        <v>0.03245</v>
-      </c>
-      <c r="AL2" s="24" t="n">
-        <v>0.039795</v>
-      </c>
-      <c r="AM2" s="23" t="n">
-        <v>0.04997</v>
-      </c>
-      <c r="AN2" s="23" t="n">
-        <v>0.0651</v>
-      </c>
-      <c r="AO2" s="24" t="n">
-        <v>0.09201</v>
-      </c>
-      <c r="AP2" s="23" t="n">
-        <v>0.02133</v>
-      </c>
-      <c r="AQ2" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="AR2" s="21" t="n">
+      <c r="X19" s="23">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="Y19" s="23">
+        <v>2.6689999999999998E-2</v>
+      </c>
+      <c r="Z19" s="23">
+        <v>2.6689999999999998E-2</v>
+      </c>
+      <c r="AA19" s="23">
+        <v>2.1329999999999998E-2</v>
+      </c>
+      <c r="AB19" s="23">
+        <v>2.1909999999999999E-2</v>
+      </c>
+      <c r="AC19" s="23">
+        <v>2.4060000000000002E-2</v>
+      </c>
+      <c r="AD19" s="23">
+        <v>2.81E-2</v>
+      </c>
+      <c r="AE19" s="23">
+        <v>3.099E-2</v>
+      </c>
+      <c r="AF19" s="23">
+        <v>3.304E-2</v>
+      </c>
+      <c r="AG19" s="23">
+        <v>3.3750000000000002E-2</v>
+      </c>
+      <c r="AH19" s="23">
+        <v>3.2559999999999999E-2</v>
+      </c>
+      <c r="AI19" s="23">
+        <v>3.159E-2</v>
+      </c>
+      <c r="AJ19" s="23">
+        <v>3.0269999999999998E-2</v>
+      </c>
+      <c r="AK19" s="24">
+        <v>3.245E-2</v>
+      </c>
+      <c r="AL19" s="24">
+        <v>3.9794999999999997E-2</v>
+      </c>
+      <c r="AM19" s="23">
+        <v>4.9970000000000001E-2</v>
+      </c>
+      <c r="AN19" s="23">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="AO19" s="24">
+        <v>9.2009999999999995E-2</v>
+      </c>
+      <c r="AP19" s="23">
+        <v>2.1329999999999998E-2</v>
+      </c>
+      <c r="AQ19" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR19" s="21">
         <v>0.04</v>
       </c>
-      <c r="AS2" s="21" t="n">
+      <c r="AS19" s="21">
         <v>0.3</v>
       </c>
-      <c r="AT2" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="AX2" s="21" t="n">
+      <c r="AT19" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="21">
+        <v>0</v>
+      </c>
+      <c r="AW19" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX19" s="21">
         <v>0.04</v>
       </c>
-      <c r="AY2" s="21" t="n">
+      <c r="AY19" s="21">
         <v>0.3</v>
       </c>
-      <c r="AZ2" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="25" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="AZ19" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA19" s="21">
+        <v>0</v>
+      </c>
+      <c r="BB19" s="21">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.78"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="10" style="0" width="8.78"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625"/>
+    <col min="6" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="1025" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:18">
       <c r="A1" s="26" t="s">
         <v>56</v>
       </c>
       <c r="B1" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="D1" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="E1" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="F1" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="G1" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="H1" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="I1" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="J1" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="K1" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="L1" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="M1" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="N1" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="O1" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="P1" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="Q1" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="R1" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="R1" s="29" t="s">
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="21" t="str">
+        <f>Main_Input!A2</f>
+        <v>JetSubmersible_can1.1</v>
+      </c>
+      <c r="B2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E2" s="0" t="n">
+      <c r="D2">
+        <v>6500</v>
+      </c>
+      <c r="E2">
         <v>0.77</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="0" t="n">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>0.2</v>
       </c>
-      <c r="I2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="0" t="n">
-        <f aca="false">M2*N2*O2*P2</f>
-        <v>0</v>
-      </c>
-      <c r="R2" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="30"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="30"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30"/>
-    </row>
-    <row r="15" s="12" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>M2*N2*O2*P2</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="21" t="str">
+        <f>Main_Input!A3</f>
+        <v>JetSubmersible_can1.2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5500</v>
+      </c>
+      <c r="E3">
+        <v>0.77</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f>M3*N3*O3*P3</f>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="21" t="str">
+        <f>Main_Input!A4</f>
+        <v>JetSubmersible_can1.3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>5500</v>
+      </c>
+      <c r="E4">
+        <v>0.77</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f>M4*N4*O4*P4</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="21" t="str">
+        <f>Main_Input!A5</f>
+        <v>JetSubmersible_can1.4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>5500</v>
+      </c>
+      <c r="E5">
+        <v>0.77</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f>M5*N5*O5*P5</f>
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="21" t="str">
+        <f>Main_Input!A6</f>
+        <v>JetSubmersible_can1.5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5500</v>
+      </c>
+      <c r="E6">
+        <v>0.77</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f>M6*N6*O6*P6</f>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="21" t="str">
+        <f>Main_Input!A7</f>
+        <v>JetSubmersible_conv1.1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>10000</v>
+      </c>
+      <c r="E7">
+        <v>0.78</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="21" t="str">
+        <f>Main_Input!A8</f>
+        <v>JetSubmersible_conv1.2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>10000</v>
+      </c>
+      <c r="E8">
+        <v>0.78</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="21" t="str">
+        <f>Main_Input!A9</f>
+        <v>JetSubmersible_conv1.3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9">
+        <v>0.78</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="21" t="str">
+        <f>Main_Input!A10</f>
+        <v>JetSubmersible_conv1.4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>10000</v>
+      </c>
+      <c r="E10">
+        <v>0.78</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="21" t="str">
+        <f>Main_Input!A11</f>
+        <v>JetSubmersible_conv1.5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>10000</v>
+      </c>
+      <c r="E11">
+        <v>0.78</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="21"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="21"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="21"/>
+    </row>
+    <row r="15" spans="1:18" s="12" customFormat="1"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B14" type="list">
-      <formula1>Lists!$A$2:$A$7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000000000000}">
+          <x14:formula1>
+            <xm:f>Lists!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>B2:B14</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="4" style="0" width="8.78"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="1025" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B3" t="s">
         <v>217</v>
       </c>
-      <c r="B3" s="0" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B4" t="s">
         <v>219</v>
       </c>
-      <c r="B4" s="0" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="B6" t="s">
         <v>222</v>
       </c>
-      <c r="B6" s="0" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="B7" t="s">
         <v>224</v>
       </c>
-      <c r="B7" s="0" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" s="30" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31" t="s">
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+    <row r="10" spans="1:2">
+      <c r="B10" s="30" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="31" t="s">
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+    <row r="12" spans="1:2">
+      <c r="B12" s="30" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="31" t="s">
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>237</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -3700,23 +8340,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.78"/>
+    <col min="1" max="1025" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Design Configurations/ASEN4138_Config_Jet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Design Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85978DB0-2775-462B-8CCE-E2F5ECB74B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78BBA41-0BCA-473F-ADB2-D86BCB2C56E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="MATERIALS" localSheetId="0">#REF!</definedName>
     <definedName name="MATERIALS">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -270,7 +270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="250">
   <si>
     <t>Worksheet</t>
   </si>
@@ -1014,6 +1014,12 @@
   </si>
   <si>
     <t>JetSubmersible_conv1.5</t>
+  </si>
+  <si>
+    <t>Initial design configs</t>
+  </si>
+  <si>
+    <t>JetSubmersible_can1</t>
   </si>
 </sst>
 </file>
@@ -3778,7 +3784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMK15"/>
+  <dimension ref="A1:AMK19"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.21875" style="7" customWidth="1"/>
@@ -3966,11 +3972,11 @@
         <v>5.5</v>
       </c>
       <c r="H2" s="7">
-        <f>F2/G2</f>
+        <f t="shared" ref="H2:H11" si="0">F2/G2</f>
         <v>7.2727272727272725</v>
       </c>
       <c r="I2" s="7">
-        <f>((G2/2)^2)*3.1415+2.5</f>
+        <f t="shared" ref="I2:I11" si="1">((G2/2)^2)*3.1415+2.5</f>
         <v>26.257593750000002</v>
       </c>
       <c r="J2" s="7">
@@ -3987,24 +3993,24 @@
         <v>1</v>
       </c>
       <c r="N2" s="7">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="O2" s="7">
-        <f>N2*2</f>
-        <v>760</v>
+        <f t="shared" ref="O2:O11" si="2">N2*2</f>
+        <v>720</v>
       </c>
       <c r="P2" s="7">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="7">
         <v>0.2</v>
       </c>
       <c r="R2" s="7">
-        <v>34</v>
+        <v>48.2</v>
       </c>
       <c r="S2" s="7">
-        <f>ATAN(TAN(R2*3.1415/180)-(1-Q2)/(2*(1+Q2)*P2))*180/3.1415</f>
-        <v>30.228351387955257</v>
+        <f>ATAN(TAN(R2*3.1415/180)-(1-Q2)/((1+Q2)*P2))*180/3.1415</f>
+        <v>38.134809329022481</v>
       </c>
       <c r="T2" s="7">
         <v>1.1000000000000001</v>
@@ -4013,7 +4019,7 @@
         <v>25</v>
       </c>
       <c r="V2" s="7">
-        <f>U2*2</f>
+        <f t="shared" ref="V2:V11" si="3">U2*2</f>
         <v>50</v>
       </c>
       <c r="W2" s="7">
@@ -4026,7 +4032,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="7">
-        <f>(2/3)*((2*U2)/((SQRT(W2*U2))*(1+X2)))*(1+X2+X2^2)/(1+X2)</f>
+        <f t="shared" ref="Z2:Z11" si="4">(2/3)*((2*U2)/((SQRT(W2*U2))*(1+X2)))*(1+X2+X2^2)/(1+X2)</f>
         <v>3.171014677825942</v>
       </c>
       <c r="AA2" s="7">
@@ -4057,7 +4063,7 @@
         <v>55</v>
       </c>
       <c r="AJ2" s="7">
-        <f>2*AI2</f>
+        <f t="shared" ref="AJ2:AJ11" si="5">2*AI2</f>
         <v>110</v>
       </c>
       <c r="AK2" s="7">
@@ -4070,7 +4076,7 @@
         <v>20</v>
       </c>
       <c r="AN2" s="7">
-        <f>(2/3)*((2*AI2)/((SQRT(AK2*AI2))*(1+AL2)))*(1+AL2+AL2^2)/(1+AL2)</f>
+        <f t="shared" ref="AN2:AN11" si="6">(2/3)*((2*AI2)/((SQRT(AK2*AI2))*(1+AL2)))*(1+AL2+AL2^2)/(1+AL2)</f>
         <v>6.9026671531786787</v>
       </c>
       <c r="AO2" s="7">
@@ -4121,11 +4127,11 @@
         <v>5.5</v>
       </c>
       <c r="H3" s="7">
-        <f>F3/G3</f>
+        <f t="shared" si="0"/>
         <v>7.2727272727272725</v>
       </c>
       <c r="I3" s="7">
-        <f>((G3/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>26.257593750000002</v>
       </c>
       <c r="J3" s="7">
@@ -4142,14 +4148,14 @@
         <v>1</v>
       </c>
       <c r="N3" s="7">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="O3" s="7">
-        <f>N3*2</f>
-        <v>720</v>
+        <f t="shared" si="2"/>
+        <v>900</v>
       </c>
       <c r="P3" s="7">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="7">
         <v>0.2</v>
@@ -4158,8 +4164,8 @@
         <v>48.2</v>
       </c>
       <c r="S3" s="7">
-        <f>ATAN(TAN(R3*3.1415/180)-(1-Q3)/(2*(1+Q3)*P3))*180/3.1415</f>
-        <v>44.036243565531883</v>
+        <f t="shared" ref="S3:S11" si="7">ATAN(TAN(R3*3.1415/180)-(1-Q3)/((1+Q3)*P3))*180/3.1415</f>
+        <v>24.310202077346343</v>
       </c>
       <c r="T3" s="7">
         <v>1.1000000000000001</v>
@@ -4168,7 +4174,7 @@
         <v>25</v>
       </c>
       <c r="V3" s="7">
-        <f>U3*2</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="W3" s="7">
@@ -4181,7 +4187,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="7">
-        <f>(2/3)*((2*U3)/((SQRT(W3*U3))*(1+X3)))*(1+X3+X3^2)/(1+X3)</f>
+        <f t="shared" si="4"/>
         <v>3.171014677825942</v>
       </c>
       <c r="AA3" s="7">
@@ -4212,7 +4218,7 @@
         <v>55</v>
       </c>
       <c r="AJ3" s="7">
-        <f>2*AI3</f>
+        <f t="shared" si="5"/>
         <v>110</v>
       </c>
       <c r="AK3" s="7">
@@ -4225,7 +4231,7 @@
         <v>20</v>
       </c>
       <c r="AN3" s="7">
-        <f>(2/3)*((2*AI3)/((SQRT(AK3*AI3))*(1+AL3)))*(1+AL3+AL3^2)/(1+AL3)</f>
+        <f t="shared" si="6"/>
         <v>6.9026671531786787</v>
       </c>
       <c r="AO3" s="7">
@@ -4276,11 +4282,11 @@
         <v>5.5</v>
       </c>
       <c r="H4" s="7">
-        <f>F4/G4</f>
+        <f t="shared" si="0"/>
         <v>7.2727272727272725</v>
       </c>
       <c r="I4" s="7">
-        <f>((G4/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>26.257593750000002</v>
       </c>
       <c r="J4" s="7">
@@ -4297,14 +4303,14 @@
         <v>1</v>
       </c>
       <c r="N4" s="7">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="O4" s="7">
-        <f>N4*2</f>
-        <v>720</v>
+        <f t="shared" si="2"/>
+        <v>800</v>
       </c>
       <c r="P4" s="7">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="7">
         <v>0.2</v>
@@ -4313,8 +4319,8 @@
         <v>48.2</v>
       </c>
       <c r="S4" s="7">
-        <f>ATAN(TAN(R4*3.1415/180)-(1-Q4)/(2*(1+Q4)*P4))*180/3.1415</f>
-        <v>44.036243565531883</v>
+        <f t="shared" si="7"/>
+        <v>24.310202077346343</v>
       </c>
       <c r="T4" s="7">
         <v>1.1000000000000001</v>
@@ -4323,7 +4329,7 @@
         <v>25</v>
       </c>
       <c r="V4" s="7">
-        <f>U4*2</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="W4" s="7">
@@ -4336,7 +4342,7 @@
         <v>32</v>
       </c>
       <c r="Z4" s="7">
-        <f>(2/3)*((2*U4)/((SQRT(W4*U4))*(1+X4)))*(1+X4+X4^2)/(1+X4)</f>
+        <f t="shared" si="4"/>
         <v>3.171014677825942</v>
       </c>
       <c r="AA4" s="7">
@@ -4367,7 +4373,7 @@
         <v>55</v>
       </c>
       <c r="AJ4" s="7">
-        <f>2*AI4</f>
+        <f t="shared" si="5"/>
         <v>110</v>
       </c>
       <c r="AK4" s="7">
@@ -4380,7 +4386,7 @@
         <v>20</v>
       </c>
       <c r="AN4" s="7">
-        <f>(2/3)*((2*AI4)/((SQRT(AK4*AI4))*(1+AL4)))*(1+AL4+AL4^2)/(1+AL4)</f>
+        <f t="shared" si="6"/>
         <v>6.9026671531786787</v>
       </c>
       <c r="AO4" s="7">
@@ -4431,11 +4437,11 @@
         <v>5.5</v>
       </c>
       <c r="H5" s="7">
-        <f>F5/G5</f>
+        <f t="shared" si="0"/>
         <v>7.2727272727272725</v>
       </c>
       <c r="I5" s="7">
-        <f>((G5/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>26.257593750000002</v>
       </c>
       <c r="J5" s="7">
@@ -4452,14 +4458,14 @@
         <v>1</v>
       </c>
       <c r="N5" s="7">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="O5" s="7">
-        <f>N5*2</f>
-        <v>720</v>
+        <f t="shared" si="2"/>
+        <v>700</v>
       </c>
       <c r="P5" s="7">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="7">
         <v>0.2</v>
@@ -4468,8 +4474,8 @@
         <v>48.2</v>
       </c>
       <c r="S5" s="7">
-        <f>ATAN(TAN(R5*3.1415/180)-(1-Q5)/(2*(1+Q5)*P5))*180/3.1415</f>
-        <v>44.036243565531883</v>
+        <f t="shared" si="7"/>
+        <v>24.310202077346343</v>
       </c>
       <c r="T5" s="7">
         <v>1.1000000000000001</v>
@@ -4478,7 +4484,7 @@
         <v>25</v>
       </c>
       <c r="V5" s="7">
-        <f>U5*2</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="W5" s="7">
@@ -4491,7 +4497,7 @@
         <v>32</v>
       </c>
       <c r="Z5" s="7">
-        <f>(2/3)*((2*U5)/((SQRT(W5*U5))*(1+X5)))*(1+X5+X5^2)/(1+X5)</f>
+        <f t="shared" si="4"/>
         <v>3.171014677825942</v>
       </c>
       <c r="AA5" s="7">
@@ -4522,7 +4528,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" s="7">
-        <f>2*AI5</f>
+        <f t="shared" si="5"/>
         <v>110</v>
       </c>
       <c r="AK5" s="7">
@@ -4535,7 +4541,7 @@
         <v>20</v>
       </c>
       <c r="AN5" s="7">
-        <f>(2/3)*((2*AI5)/((SQRT(AK5*AI5))*(1+AL5)))*(1+AL5+AL5^2)/(1+AL5)</f>
+        <f t="shared" si="6"/>
         <v>6.9026671531786787</v>
       </c>
       <c r="AO5" s="7">
@@ -4586,11 +4592,11 @@
         <v>5.5</v>
       </c>
       <c r="H6" s="7">
-        <f>F6/G6</f>
+        <f t="shared" si="0"/>
         <v>7.2727272727272725</v>
       </c>
       <c r="I6" s="7">
-        <f>((G6/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>26.257593750000002</v>
       </c>
       <c r="J6" s="7">
@@ -4607,14 +4613,14 @@
         <v>1</v>
       </c>
       <c r="N6" s="7">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="O6" s="7">
-        <f>N6*2</f>
-        <v>720</v>
+        <f t="shared" si="2"/>
+        <v>600</v>
       </c>
       <c r="P6" s="7">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="7">
         <v>0.2</v>
@@ -4623,8 +4629,8 @@
         <v>48.2</v>
       </c>
       <c r="S6" s="7">
-        <f>ATAN(TAN(R6*3.1415/180)-(1-Q6)/(2*(1+Q6)*P6))*180/3.1415</f>
-        <v>44.036243565531883</v>
+        <f t="shared" si="7"/>
+        <v>24.310202077346343</v>
       </c>
       <c r="T6" s="7">
         <v>1.1000000000000001</v>
@@ -4633,7 +4639,7 @@
         <v>25</v>
       </c>
       <c r="V6" s="7">
-        <f>U6*2</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="W6" s="7">
@@ -4646,7 +4652,7 @@
         <v>32</v>
       </c>
       <c r="Z6" s="7">
-        <f>(2/3)*((2*U6)/((SQRT(W6*U6))*(1+X6)))*(1+X6+X6^2)/(1+X6)</f>
+        <f t="shared" si="4"/>
         <v>3.171014677825942</v>
       </c>
       <c r="AA6" s="7">
@@ -4677,7 +4683,7 @@
         <v>55</v>
       </c>
       <c r="AJ6" s="7">
-        <f>2*AI6</f>
+        <f t="shared" si="5"/>
         <v>110</v>
       </c>
       <c r="AK6" s="7">
@@ -4690,7 +4696,7 @@
         <v>20</v>
       </c>
       <c r="AN6" s="7">
-        <f>(2/3)*((2*AI6)/((SQRT(AK6*AI6))*(1+AL6)))*(1+AL6+AL6^2)/(1+AL6)</f>
+        <f t="shared" si="6"/>
         <v>6.9026671531786787</v>
       </c>
       <c r="AO6" s="7">
@@ -4741,11 +4747,11 @@
         <v>4.5</v>
       </c>
       <c r="H7" s="7">
-        <f>F7/G7</f>
+        <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
       <c r="I7" s="7">
-        <f>((G7/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>18.40384375</v>
       </c>
       <c r="J7" s="7">
@@ -4765,7 +4771,7 @@
         <v>310</v>
       </c>
       <c r="O7" s="7">
-        <f>N7*2</f>
+        <f t="shared" si="2"/>
         <v>620</v>
       </c>
       <c r="P7" s="7">
@@ -4778,8 +4784,8 @@
         <v>44</v>
       </c>
       <c r="S7" s="7">
-        <f>ATAN(TAN(R7*3.1415/180)-(1-Q7)/(2*(1+Q7)*P7))*180/3.1415</f>
-        <v>40.208174924683249</v>
+        <f t="shared" si="7"/>
+        <v>35.939576280851796</v>
       </c>
       <c r="T7" s="7">
         <v>1.1000000000000001</v>
@@ -4788,7 +4794,7 @@
         <v>10</v>
       </c>
       <c r="V7" s="7">
-        <f>U7*2</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="W7" s="7">
@@ -4801,7 +4807,7 @@
         <v>31</v>
       </c>
       <c r="Z7" s="7">
-        <f>(2/3)*((2*U7)/((SQRT(W7*U7))*(1+X7)))*(1+X7+X7^2)/(1+X7)</f>
+        <f t="shared" si="4"/>
         <v>1.6237266827246648</v>
       </c>
       <c r="AA7" s="7">
@@ -4832,7 +4838,7 @@
         <v>17</v>
       </c>
       <c r="AJ7" s="7">
-        <f>2*AI7</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="AK7" s="7">
@@ -4845,7 +4851,7 @@
         <v>20</v>
       </c>
       <c r="AN7" s="7">
-        <f>(2/3)*((2*AI7)/((SQRT(AK7*AI7))*(1+AL7)))*(1+AL7+AL7^2)/(1+AL7)</f>
+        <f t="shared" si="6"/>
         <v>3.2613354542804762</v>
       </c>
       <c r="AO7" s="7">
@@ -4896,11 +4902,11 @@
         <v>4.5</v>
       </c>
       <c r="H8" s="7">
-        <f>F8/G8</f>
+        <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
       <c r="I8" s="7">
-        <f>((G8/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>18.40384375</v>
       </c>
       <c r="J8" s="7">
@@ -4920,7 +4926,7 @@
         <v>310</v>
       </c>
       <c r="O8" s="7">
-        <f>N8*2</f>
+        <f t="shared" si="2"/>
         <v>620</v>
       </c>
       <c r="P8" s="7">
@@ -4933,8 +4939,8 @@
         <v>44</v>
       </c>
       <c r="S8" s="7">
-        <f>ATAN(TAN(R8*3.1415/180)-(1-Q8)/(2*(1+Q8)*P8))*180/3.1415</f>
-        <v>40.208174924683249</v>
+        <f t="shared" si="7"/>
+        <v>35.939576280851796</v>
       </c>
       <c r="T8" s="7">
         <v>1.1000000000000001</v>
@@ -4943,7 +4949,7 @@
         <v>10</v>
       </c>
       <c r="V8" s="7">
-        <f>U8*2</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="W8" s="7">
@@ -4956,7 +4962,7 @@
         <v>31</v>
       </c>
       <c r="Z8" s="7">
-        <f>(2/3)*((2*U8)/((SQRT(W8*U8))*(1+X8)))*(1+X8+X8^2)/(1+X8)</f>
+        <f t="shared" si="4"/>
         <v>1.6237266827246648</v>
       </c>
       <c r="AA8" s="7">
@@ -4987,7 +4993,7 @@
         <v>17</v>
       </c>
       <c r="AJ8" s="7">
-        <f>2*AI8</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="AK8" s="7">
@@ -5000,7 +5006,7 @@
         <v>20</v>
       </c>
       <c r="AN8" s="7">
-        <f>(2/3)*((2*AI8)/((SQRT(AK8*AI8))*(1+AL8)))*(1+AL8+AL8^2)/(1+AL8)</f>
+        <f t="shared" si="6"/>
         <v>3.2613354542804762</v>
       </c>
       <c r="AO8" s="7">
@@ -5051,11 +5057,11 @@
         <v>4.5</v>
       </c>
       <c r="H9" s="7">
-        <f>F9/G9</f>
+        <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
       <c r="I9" s="7">
-        <f>((G9/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>18.40384375</v>
       </c>
       <c r="J9" s="7">
@@ -5075,7 +5081,7 @@
         <v>310</v>
       </c>
       <c r="O9" s="7">
-        <f>N9*2</f>
+        <f t="shared" si="2"/>
         <v>620</v>
       </c>
       <c r="P9" s="7">
@@ -5088,8 +5094,8 @@
         <v>44</v>
       </c>
       <c r="S9" s="7">
-        <f>ATAN(TAN(R9*3.1415/180)-(1-Q9)/(2*(1+Q9)*P9))*180/3.1415</f>
-        <v>40.208174924683249</v>
+        <f t="shared" si="7"/>
+        <v>35.939576280851796</v>
       </c>
       <c r="T9" s="7">
         <v>1.1000000000000001</v>
@@ -5098,7 +5104,7 @@
         <v>10</v>
       </c>
       <c r="V9" s="7">
-        <f>U9*2</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="W9" s="7">
@@ -5111,7 +5117,7 @@
         <v>31</v>
       </c>
       <c r="Z9" s="7">
-        <f>(2/3)*((2*U9)/((SQRT(W9*U9))*(1+X9)))*(1+X9+X9^2)/(1+X9)</f>
+        <f t="shared" si="4"/>
         <v>1.6237266827246648</v>
       </c>
       <c r="AA9" s="7">
@@ -5142,7 +5148,7 @@
         <v>17</v>
       </c>
       <c r="AJ9" s="7">
-        <f>2*AI9</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="AK9" s="7">
@@ -5155,7 +5161,7 @@
         <v>20</v>
       </c>
       <c r="AN9" s="7">
-        <f>(2/3)*((2*AI9)/((SQRT(AK9*AI9))*(1+AL9)))*(1+AL9+AL9^2)/(1+AL9)</f>
+        <f t="shared" si="6"/>
         <v>3.2613354542804762</v>
       </c>
       <c r="AO9" s="7">
@@ -5206,11 +5212,11 @@
         <v>4.5</v>
       </c>
       <c r="H10" s="7">
-        <f>F10/G10</f>
+        <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
       <c r="I10" s="7">
-        <f>((G10/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>18.40384375</v>
       </c>
       <c r="J10" s="7">
@@ -5230,7 +5236,7 @@
         <v>310</v>
       </c>
       <c r="O10" s="7">
-        <f>N10*2</f>
+        <f t="shared" si="2"/>
         <v>620</v>
       </c>
       <c r="P10" s="7">
@@ -5243,8 +5249,8 @@
         <v>44</v>
       </c>
       <c r="S10" s="7">
-        <f>ATAN(TAN(R10*3.1415/180)-(1-Q10)/(2*(1+Q10)*P10))*180/3.1415</f>
-        <v>40.208174924683249</v>
+        <f t="shared" si="7"/>
+        <v>35.939576280851796</v>
       </c>
       <c r="T10" s="7">
         <v>1.1000000000000001</v>
@@ -5253,7 +5259,7 @@
         <v>10</v>
       </c>
       <c r="V10" s="7">
-        <f>U10*2</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="W10" s="7">
@@ -5266,7 +5272,7 @@
         <v>31</v>
       </c>
       <c r="Z10" s="7">
-        <f>(2/3)*((2*U10)/((SQRT(W10*U10))*(1+X10)))*(1+X10+X10^2)/(1+X10)</f>
+        <f t="shared" si="4"/>
         <v>1.6237266827246648</v>
       </c>
       <c r="AA10" s="7">
@@ -5297,7 +5303,7 @@
         <v>17</v>
       </c>
       <c r="AJ10" s="7">
-        <f>2*AI10</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="AK10" s="7">
@@ -5310,7 +5316,7 @@
         <v>20</v>
       </c>
       <c r="AN10" s="7">
-        <f>(2/3)*((2*AI10)/((SQRT(AK10*AI10))*(1+AL10)))*(1+AL10+AL10^2)/(1+AL10)</f>
+        <f t="shared" si="6"/>
         <v>3.2613354542804762</v>
       </c>
       <c r="AO10" s="7">
@@ -5361,11 +5367,11 @@
         <v>4.5</v>
       </c>
       <c r="H11" s="7">
-        <f>F11/G11</f>
+        <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
       <c r="I11" s="7">
-        <f>((G11/2)^2)*3.1415+2.5</f>
+        <f t="shared" si="1"/>
         <v>18.40384375</v>
       </c>
       <c r="J11" s="7">
@@ -5385,7 +5391,7 @@
         <v>310</v>
       </c>
       <c r="O11" s="7">
-        <f>N11*2</f>
+        <f t="shared" si="2"/>
         <v>620</v>
       </c>
       <c r="P11" s="7">
@@ -5398,8 +5404,8 @@
         <v>44</v>
       </c>
       <c r="S11" s="7">
-        <f>ATAN(TAN(R11*3.1415/180)-(1-Q11)/(2*(1+Q11)*P11))*180/3.1415</f>
-        <v>40.208174924683249</v>
+        <f t="shared" si="7"/>
+        <v>35.939576280851796</v>
       </c>
       <c r="T11" s="7">
         <v>1.1000000000000001</v>
@@ -5408,7 +5414,7 @@
         <v>10</v>
       </c>
       <c r="V11" s="7">
-        <f>U11*2</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="W11" s="7">
@@ -5421,7 +5427,7 @@
         <v>31</v>
       </c>
       <c r="Z11" s="7">
-        <f>(2/3)*((2*U11)/((SQRT(W11*U11))*(1+X11)))*(1+X11+X11^2)/(1+X11)</f>
+        <f t="shared" si="4"/>
         <v>1.6237266827246648</v>
       </c>
       <c r="AA11" s="7">
@@ -5452,7 +5458,7 @@
         <v>17</v>
       </c>
       <c r="AJ11" s="7">
-        <f>2*AI11</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="AK11" s="7">
@@ -5465,7 +5471,7 @@
         <v>20</v>
       </c>
       <c r="AN11" s="7">
-        <f>(2/3)*((2*AI11)/((SQRT(AK11*AI11))*(1+AL11)))*(1+AL11+AL11^2)/(1+AL11)</f>
+        <f t="shared" si="6"/>
         <v>3.2613354542804762</v>
       </c>
       <c r="AO11" s="7">
@@ -5494,6 +5500,476 @@
       </c>
     </row>
     <row r="15" spans="1:48" s="20" customFormat="1"/>
+    <row r="16" spans="1:48">
+      <c r="A16" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:48">
+      <c r="A17" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7">
+        <v>45</v>
+      </c>
+      <c r="G17" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" ref="H17" si="8">F17/G17</f>
+        <v>8.1818181818181817</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" ref="I17" si="9">((G17/2)^2)*3.1415+2.5</f>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7">
+        <f>(F17)*G17*3.1415*0.9</f>
+        <v>699.76912500000003</v>
+      </c>
+      <c r="L17" s="7">
+        <v>1</v>
+      </c>
+      <c r="M17" s="7">
+        <v>1</v>
+      </c>
+      <c r="N17" s="7">
+        <v>450</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" ref="O17" si="10">N17*2</f>
+        <v>900</v>
+      </c>
+      <c r="P17" s="7">
+        <v>3.63</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R17" s="7">
+        <v>34</v>
+      </c>
+      <c r="S17" s="7">
+        <f>ATAN(TAN(R17*3.1415/180)-(1-Q17)/((1+Q17)*P17))*180/3.1415</f>
+        <v>26.143883229632934</v>
+      </c>
+      <c r="T17" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U17" s="7">
+        <v>25</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" ref="V17" si="11">U17*2</f>
+        <v>50</v>
+      </c>
+      <c r="W17" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="X17" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="Y17" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" ref="Z17" si="12">(2/3)*((2*U17)/((SQRT(W17*U17))*(1+X17)))*(1+X17+X17^2)/(1+X17)</f>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA17" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ17" s="7">
+        <f t="shared" ref="AJ17" si="13">2*AI17</f>
+        <v>110</v>
+      </c>
+      <c r="AK17" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="AL17" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM17" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN17" s="7">
+        <f t="shared" ref="AN17" si="14">(2/3)*((2*AI17)/((SQRT(AK17*AI17))*(1+AL17)))*(1+AL17+AL17^2)/(1+AL17)</f>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO17" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:48">
+      <c r="A18" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7">
+        <v>40</v>
+      </c>
+      <c r="G18" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" ref="H18:H19" si="15">F18/G18</f>
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" ref="I18:I19" si="16">((G18/2)^2)*3.1415+2.5</f>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J18" s="7">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7">
+        <f>(F18)*G18*3.1415*0.9</f>
+        <v>622.01700000000005</v>
+      </c>
+      <c r="L18" s="7">
+        <v>1</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1</v>
+      </c>
+      <c r="N18" s="7">
+        <v>380</v>
+      </c>
+      <c r="O18" s="7">
+        <f t="shared" ref="O18:O19" si="17">N18*2</f>
+        <v>760</v>
+      </c>
+      <c r="P18" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R18" s="7">
+        <v>34</v>
+      </c>
+      <c r="S18" s="7">
+        <f t="shared" ref="S18:S19" si="18">ATAN(TAN(R18*3.1415/180)-(1-Q18)/((1+Q18)*P18))*180/3.1415</f>
+        <v>20.378253616689143</v>
+      </c>
+      <c r="T18" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U18" s="7">
+        <v>25</v>
+      </c>
+      <c r="V18" s="7">
+        <f t="shared" ref="V18:V19" si="19">U18*2</f>
+        <v>50</v>
+      </c>
+      <c r="W18" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="X18" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="Y18" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z18" s="7">
+        <f t="shared" ref="Z18:Z19" si="20">(2/3)*((2*U18)/((SQRT(W18*U18))*(1+X18)))*(1+X18+X18^2)/(1+X18)</f>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA18" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ18" s="7">
+        <f t="shared" ref="AJ18:AJ19" si="21">2*AI18</f>
+        <v>110</v>
+      </c>
+      <c r="AK18" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="AL18" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM18" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN18" s="7">
+        <f t="shared" ref="AN18:AN19" si="22">(2/3)*((2*AI18)/((SQRT(AK18*AI18))*(1+AL18)))*(1+AL18+AL18^2)/(1+AL18)</f>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO18" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:48">
+      <c r="A19" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7">
+        <v>40</v>
+      </c>
+      <c r="G19" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="15"/>
+        <v>7.2727272727272725</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="16"/>
+        <v>26.257593750000002</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7">
+        <f>(F19)*G19*3.1415*0.9</f>
+        <v>622.01700000000005</v>
+      </c>
+      <c r="L19" s="7">
+        <v>1</v>
+      </c>
+      <c r="M19" s="7">
+        <v>1</v>
+      </c>
+      <c r="N19" s="7">
+        <v>360</v>
+      </c>
+      <c r="O19" s="7">
+        <f t="shared" si="17"/>
+        <v>720</v>
+      </c>
+      <c r="P19" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R19" s="7">
+        <v>48.2</v>
+      </c>
+      <c r="S19" s="7">
+        <f t="shared" si="18"/>
+        <v>39.193340519780634</v>
+      </c>
+      <c r="T19" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U19" s="7">
+        <v>25</v>
+      </c>
+      <c r="V19" s="7">
+        <f t="shared" si="19"/>
+        <v>50</v>
+      </c>
+      <c r="W19" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="X19" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="Y19" s="7">
+        <v>32</v>
+      </c>
+      <c r="Z19" s="7">
+        <f t="shared" si="20"/>
+        <v>3.171014677825942</v>
+      </c>
+      <c r="AA19" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="7">
+        <v>55</v>
+      </c>
+      <c r="AJ19" s="7">
+        <f t="shared" si="21"/>
+        <v>110</v>
+      </c>
+      <c r="AK19" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="AL19" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="AM19" s="7">
+        <v>20</v>
+      </c>
+      <c r="AN19" s="7">
+        <f t="shared" si="22"/>
+        <v>6.9026671531786787</v>
+      </c>
+      <c r="AO19" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5507,7 +5983,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>B2:B14</xm:sqref>
+          <xm:sqref>B2:B14 B17:B19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7523,7 +7999,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -8179,6 +8655,125 @@
       <c r="A14" s="21"/>
     </row>
     <row r="15" spans="1:18" s="12" customFormat="1"/>
+    <row r="16" spans="1:18">
+      <c r="A16" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>6500</v>
+      </c>
+      <c r="E17">
+        <v>0.77</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <f>M17*N17*O17*P17</f>
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>5500</v>
+      </c>
+      <c r="E18">
+        <v>0.77</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <f>M18*N18*O18*P18</f>
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
